--- a/data/expectations/Vaentingar_markadsadila.xlsx
+++ b/data/expectations/Vaentingar_markadsadila.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29910"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\HAGFRAEDISVID\Innlendir fjármálamarkaðir\4. Markaðskönnun\2025\Q4 3.-5. nóvember\B3. Excel skjal fyrir vef - birtingarskjal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\HAGFRAEDISVID\Innlendir fjármálamarkaðir\4. Markaðskönnun\2026\Q1 19. -21. janúar\B3. Excel skjal fyrir vef - birtingarskjal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C799E66-594B-4D17-A2E5-F699C57A22E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{544A60B5-DA87-4BEE-A3EA-2D591F780E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Efnisyfirlit_Contents" sheetId="11" r:id="rId1"/>
@@ -26,8 +26,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">I!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">II!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,6 +39,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,585 +47,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="218">
-  <si>
-    <t>2012Q1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="220">
   <si>
     <t>Seðlabanki Íslands / Central Bank of Iceland</t>
   </si>
   <si>
-    <t xml:space="preserve">      Staðalfrávik / standard deviation</t>
+    <t>Birtingardagur / Date of publication: 28/1/2026</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Væntingakönnun markaðsaðila / Market expectations survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What do you think twelve-month inflation will measure, on average, in each quarter?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the long-term nominal interest rate be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the long-term real interest rate be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be 24 months from now?</t>
-  </si>
-  <si>
-    <t>What do you think inflation will measure, on average, in each quarter?</t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be 12 months from now?</t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t>Væntingar til skamms tíma / Short-term expectations</t>
-  </si>
-  <si>
-    <t>Væntingar til langs tíma / Long-term expectations</t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Miðgildi / median</t>
-  </si>
-  <si>
-    <t>Long-term expectations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 12 mánuði? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 24 mánuði? </t>
-  </si>
-  <si>
-    <t>Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 5 ár? </t>
-  </si>
-  <si>
-    <t>Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 10 ár?</t>
-  </si>
-  <si>
-    <t>Væntingar til langs tíma</t>
-  </si>
-  <si>
-    <t>Heimild: Seðlabanki Íslands / Source: Central Bank of Iceland</t>
-  </si>
-  <si>
-    <t>Meðaltal /average</t>
-  </si>
-  <si>
-    <t>+1Q</t>
-  </si>
-  <si>
-    <t>+2Q</t>
-  </si>
-  <si>
-    <t>+3Q</t>
-  </si>
-  <si>
-    <t>+4Q</t>
-  </si>
-  <si>
-    <t>Miðgildi /median</t>
-  </si>
-  <si>
-    <t>Staðalfrávik /standard deviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Meðaltal / average</t>
-  </si>
-  <si>
-    <t>núverandi ársfjórðungur / current quarter</t>
-  </si>
-  <si>
-    <t>2012Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What is your perception of the current monetary policy stance?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Hæfilegt / appropriate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 12 months from now?</t>
-  </si>
-  <si>
-    <t>2012Q3</t>
-  </si>
-  <si>
-    <t>Svarhlutfall / Participation rate</t>
-  </si>
-  <si>
-    <t>2012Q4</t>
-  </si>
-  <si>
-    <t>ISK/EUR</t>
-  </si>
-  <si>
-    <t>2013Q1</t>
-  </si>
-  <si>
-    <t>2013Q2</t>
-  </si>
-  <si>
-    <t>2013Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Of laust / too loose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Of þétt /  too tight</t>
-  </si>
-  <si>
-    <t>2013Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Alltof laust / far too loose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Alltof þétt / far too tight</t>
-  </si>
-  <si>
-    <t>2014Q1</t>
-  </si>
-  <si>
-    <t>2014Q2</t>
-  </si>
-  <si>
-    <t>2014Q3</t>
-  </si>
-  <si>
-    <t>2014Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t>2015Q1</t>
-  </si>
-  <si>
-    <t>2015Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? </t>
-  </si>
-  <si>
-    <t>What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 2 / Question 2: </t>
-  </si>
-  <si>
-    <t>2015Q3</t>
-  </si>
-  <si>
-    <t>Meðaltal / average</t>
-  </si>
-  <si>
-    <t>Miðgildi / median</t>
-  </si>
-  <si>
-    <t>Staðalfrávik / standard deviation</t>
-  </si>
-  <si>
-    <t>2015Q4</t>
-  </si>
-  <si>
-    <t>2016Q1</t>
-  </si>
-  <si>
-    <t>2016Q2</t>
-  </si>
-  <si>
-    <t>2016Q3</t>
-  </si>
-  <si>
-    <t>2016Q4</t>
-  </si>
-  <si>
-    <t>2017Q1</t>
-  </si>
-  <si>
-    <t>2017Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 1/ Question 1: </t>
-  </si>
-  <si>
-    <t>Væntingar til skamms og meðallangs tíma</t>
-  </si>
-  <si>
-    <t>III-a</t>
-  </si>
-  <si>
-    <t>III-b</t>
-  </si>
-  <si>
-    <t>III-c</t>
-  </si>
-  <si>
-    <t>Short- and medium term expectations</t>
-  </si>
-  <si>
-    <t>Álit á taumhaldi peningastefnu Seðlabanka Íslands</t>
-  </si>
-  <si>
-    <t>Álit á taumhalds peningastefnu Seðlabanka Íslands / Opinion of the Central Bank of Iceland‘s monetary stance</t>
-  </si>
-  <si>
-    <t>Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir?</t>
-  </si>
-  <si>
-    <t>Spurning 5 / Question 5:</t>
-  </si>
-  <si>
-    <t>What is your perception of the current monetary policy stance?</t>
-  </si>
-  <si>
-    <t>Opinion of the Central Bank of Iceland‘s monetary stance</t>
-  </si>
-  <si>
-    <t>Væntingar til skamms og meðallangs tíma / Short- and medium-term expectations</t>
-  </si>
-  <si>
-    <t>Spurning 3a / Question 3a:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á  stöðu ársverðbólgu eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Hver er þín skoðun á gengi evru gagnvart krónu eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 3b / Question 3b: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu ársverðbólgu eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á gengi evru gagnvart krónu eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 3c / Question 3c: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 5 ár? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Hvað telur þú að skammtímanafnvextir verði að meðaltali næstu 5 ár? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að skammtímaraunvextir verði að meðaltali næstu 5 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 10 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að langtímanafnvextir verði að meðaltali næstu 10 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að langtímaraunvextir verði að meðaltali næstu 10 ár? /</t>
-  </si>
-  <si>
-    <t>Spurning 4 / Question 4:</t>
-  </si>
-  <si>
-    <t>2017Q3</t>
-  </si>
-  <si>
-    <t>2017Q4</t>
-  </si>
-  <si>
-    <t>2018Q1</t>
-  </si>
-  <si>
-    <t>2018Q2</t>
-  </si>
-  <si>
-    <t>2018Q3</t>
-  </si>
-  <si>
-    <t>2018Q4</t>
-  </si>
-  <si>
-    <t>2019Q1</t>
-  </si>
-  <si>
-    <t>2019Q2</t>
-  </si>
-  <si>
-    <t>2019Q3</t>
-  </si>
-  <si>
-    <t>Dagsetningar / Dates</t>
-  </si>
-  <si>
-    <t>2019Q4</t>
-  </si>
-  <si>
-    <t>2020Q1</t>
-  </si>
-  <si>
-    <t>2020Q2</t>
-  </si>
-  <si>
-    <t>2020Q3</t>
-  </si>
-  <si>
-    <t>2020Q4</t>
-  </si>
-  <si>
-    <t>2021Q1</t>
-  </si>
-  <si>
-    <t>2021Q2</t>
-  </si>
-  <si>
-    <t>2021Q3</t>
-  </si>
-  <si>
-    <t>2021Q4</t>
-  </si>
-  <si>
-    <t>2022Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 24 months from now?</t>
-  </si>
-  <si>
-    <t>2022Q2</t>
-  </si>
-  <si>
-    <t>2022Q3</t>
-  </si>
-  <si>
-    <t>2022Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>2023Q1</t>
-  </si>
-  <si>
-    <t>2023Q2</t>
-  </si>
-  <si>
-    <t>13.-17. feb. 2012</t>
-  </si>
-  <si>
-    <t>7.-11. maí 2012</t>
-  </si>
-  <si>
-    <t>13.-17. ágú. 2012</t>
-  </si>
-  <si>
-    <t>5.-9. nóv 2012</t>
-  </si>
-  <si>
-    <t>29. jan.-1. feb. 2013</t>
-  </si>
-  <si>
-    <t>6.-10. maí 2013</t>
-  </si>
-  <si>
-    <t>12.-15. ágúst 2013</t>
-  </si>
-  <si>
-    <t>28.-30. október 2013</t>
-  </si>
-  <si>
-    <t>3.-5. febrúar 2014</t>
-  </si>
-  <si>
-    <t>12.-14. maí 2014</t>
-  </si>
-  <si>
-    <t>11.-14 ágúst 2014</t>
-  </si>
-  <si>
-    <t>29.-31 október 2014</t>
-  </si>
-  <si>
-    <t>29.-30. janúar 2015</t>
-  </si>
-  <si>
-    <t>4.-6. maí 2015</t>
-  </si>
-  <si>
-    <t>10.-13. ágúst 2015</t>
-  </si>
-  <si>
-    <t>29. okt.-2. nóv. 2015</t>
-  </si>
-  <si>
-    <t>1.-3. febrúar 2016</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2016</t>
-  </si>
-  <si>
-    <t>8.-10. ágúst 2016</t>
-  </si>
-  <si>
-    <t>31. okt.-2. nóv. 2016</t>
-  </si>
-  <si>
-    <t>30. jan.-1. feb. 2017</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2017</t>
-  </si>
-  <si>
-    <t>9.-11. ágúst 2017</t>
-  </si>
-  <si>
-    <t>30. okt.-1. nóv. 2017</t>
-  </si>
-  <si>
-    <t>29.-31. janúar 2018</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2018</t>
-  </si>
-  <si>
-    <t>13.-15. ágúst 2018</t>
-  </si>
-  <si>
-    <t>29.-31. október 2018</t>
-  </si>
-  <si>
-    <t>21.-23. janúar 2019</t>
-  </si>
-  <si>
-    <t>6.-8. maí 2019</t>
-  </si>
-  <si>
-    <t>12.-14. ágúst 2019</t>
-  </si>
-  <si>
-    <t>21.-23. október 2019</t>
-  </si>
-  <si>
-    <t>20.-22. janúar 2020</t>
-  </si>
-  <si>
-    <t>4.-6. maí 2020</t>
-  </si>
-  <si>
-    <t>10.-12. ágúst 2020</t>
-  </si>
-  <si>
-    <t>2.-4. nóvember 2020</t>
-  </si>
-  <si>
-    <t>18.-20. janúar 2021</t>
-  </si>
-  <si>
-    <t>3.-5. maí 2021</t>
-  </si>
-  <si>
-    <t>9.-11. ágúst 2021</t>
-  </si>
-  <si>
-    <t>1.-3. nóvember 2021</t>
-  </si>
-  <si>
-    <t>24.-26. janúar 2022</t>
-  </si>
-  <si>
-    <t>19.-22. apríl 2022</t>
-  </si>
-  <si>
-    <t>8.-10. ágúst 2022</t>
-  </si>
-  <si>
-    <t>7.-9. nóvember 2022</t>
-  </si>
-  <si>
-    <t>23.-25. janúar 2023</t>
-  </si>
-  <si>
-    <t>8.-10. maí 2023</t>
+    <r>
+      <t>Örk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / Sheet</t>
+    </r>
   </si>
   <si>
     <r>
@@ -638,23 +82,367 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Örk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / Sheet</t>
-    </r>
+    <t>Væntingar til skamms og meðallangs tíma</t>
   </si>
   <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 12 mánuði? / </t>
+    <t>Short- and medium term expectations</t>
   </si>
   <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 12 mánuði? / </t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi?</t>
+  </si>
+  <si>
+    <t>What do you think inflation will measure, on average, in each quarter?</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? </t>
+  </si>
+  <si>
+    <t>What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
+  </si>
+  <si>
+    <t>III-a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 12 mánuði? </t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be 12 months from now?</t>
+  </si>
+  <si>
+    <t>III-b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 24 mánuði? </t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be 24 months from now?</t>
+  </si>
+  <si>
+    <t>III-c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 5 ár? </t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t>Væntingar til langs tíma</t>
+  </si>
+  <si>
+    <t>Long-term expectations</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 10 ár?</t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t>Álit á taumhaldi peningastefnu Seðlabanka Íslands</t>
+  </si>
+  <si>
+    <t>Opinion of the Central Bank of Iceland‘s monetary stance</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir?</t>
+  </si>
+  <si>
+    <t>What is your perception of the current monetary policy stance?</t>
+  </si>
+  <si>
+    <t>Svarhlutfall / Participation rate</t>
+  </si>
+  <si>
+    <t>Dagsetningar / Dates</t>
+  </si>
+  <si>
+    <t>2012Q1</t>
+  </si>
+  <si>
+    <t>13.-17. feb. 2012</t>
+  </si>
+  <si>
+    <t>2012Q2</t>
+  </si>
+  <si>
+    <t>7.-11. maí 2012</t>
+  </si>
+  <si>
+    <t>2012Q3</t>
+  </si>
+  <si>
+    <t>13.-17. ágú. 2012</t>
+  </si>
+  <si>
+    <t>2012Q4</t>
+  </si>
+  <si>
+    <t>5.-9. nóv 2012</t>
+  </si>
+  <si>
+    <t>2013Q1</t>
+  </si>
+  <si>
+    <t>29. jan.-1. feb. 2013</t>
+  </si>
+  <si>
+    <t>2013Q2</t>
+  </si>
+  <si>
+    <t>6.-10. maí 2013</t>
+  </si>
+  <si>
+    <t>2013Q3</t>
+  </si>
+  <si>
+    <t>12.-15. ágúst 2013</t>
+  </si>
+  <si>
+    <t>2013Q4</t>
+  </si>
+  <si>
+    <t>28.-30. október 2013</t>
+  </si>
+  <si>
+    <t>2014Q1</t>
+  </si>
+  <si>
+    <t>3.-5. febrúar 2014</t>
+  </si>
+  <si>
+    <t>2014Q2</t>
+  </si>
+  <si>
+    <t>12.-14. maí 2014</t>
+  </si>
+  <si>
+    <t>2014Q3</t>
+  </si>
+  <si>
+    <t>11.-14 ágúst 2014</t>
+  </si>
+  <si>
+    <t>2014Q4</t>
+  </si>
+  <si>
+    <t>29.-31 október 2014</t>
+  </si>
+  <si>
+    <t>2015Q1</t>
+  </si>
+  <si>
+    <t>29.-30. janúar 2015</t>
+  </si>
+  <si>
+    <t>2015Q2</t>
+  </si>
+  <si>
+    <t>4.-6. maí 2015</t>
+  </si>
+  <si>
+    <t>2015Q3</t>
+  </si>
+  <si>
+    <t>10.-13. ágúst 2015</t>
+  </si>
+  <si>
+    <t>2015Q4</t>
+  </si>
+  <si>
+    <t>29. okt.-2. nóv. 2015</t>
+  </si>
+  <si>
+    <t>2016Q1</t>
+  </si>
+  <si>
+    <t>1.-3. febrúar 2016</t>
+  </si>
+  <si>
+    <t>2016Q2</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2016</t>
+  </si>
+  <si>
+    <t>2016Q3</t>
+  </si>
+  <si>
+    <t>8.-10. ágúst 2016</t>
+  </si>
+  <si>
+    <t>2016Q4</t>
+  </si>
+  <si>
+    <t>31. okt.-2. nóv. 2016</t>
+  </si>
+  <si>
+    <t>2017Q1</t>
+  </si>
+  <si>
+    <t>30. jan.-1. feb. 2017</t>
+  </si>
+  <si>
+    <t>2017Q2</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2017</t>
+  </si>
+  <si>
+    <t>2017Q3</t>
+  </si>
+  <si>
+    <t>9.-11. ágúst 2017</t>
+  </si>
+  <si>
+    <t>2017Q4</t>
+  </si>
+  <si>
+    <t>30. okt.-1. nóv. 2017</t>
+  </si>
+  <si>
+    <t>2018Q1</t>
+  </si>
+  <si>
+    <t>29.-31. janúar 2018</t>
+  </si>
+  <si>
+    <t>2018Q2</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2018</t>
+  </si>
+  <si>
+    <t>2018Q3</t>
+  </si>
+  <si>
+    <t>13.-15. ágúst 2018</t>
+  </si>
+  <si>
+    <t>2018Q4</t>
+  </si>
+  <si>
+    <t>29.-31. október 2018</t>
+  </si>
+  <si>
+    <t>2019Q1</t>
+  </si>
+  <si>
+    <t>21.-23. janúar 2019</t>
+  </si>
+  <si>
+    <t>2019Q2</t>
+  </si>
+  <si>
+    <t>6.-8. maí 2019</t>
+  </si>
+  <si>
+    <t>2019Q3</t>
+  </si>
+  <si>
+    <t>12.-14. ágúst 2019</t>
+  </si>
+  <si>
+    <t>2019Q4</t>
+  </si>
+  <si>
+    <t>21.-23. október 2019</t>
+  </si>
+  <si>
+    <t>2020Q1</t>
+  </si>
+  <si>
+    <t>20.-22. janúar 2020</t>
+  </si>
+  <si>
+    <t>2020Q2</t>
+  </si>
+  <si>
+    <t>4.-6. maí 2020</t>
+  </si>
+  <si>
+    <t>2020Q3</t>
+  </si>
+  <si>
+    <t>10.-12. ágúst 2020</t>
+  </si>
+  <si>
+    <t>2020Q4</t>
+  </si>
+  <si>
+    <t>2.-4. nóvember 2020</t>
+  </si>
+  <si>
+    <t>2021Q1</t>
+  </si>
+  <si>
+    <t>18.-20. janúar 2021</t>
+  </si>
+  <si>
+    <t>2021Q2</t>
+  </si>
+  <si>
+    <t>3.-5. maí 2021</t>
+  </si>
+  <si>
+    <t>2021Q3</t>
+  </si>
+  <si>
+    <t>9.-11. ágúst 2021</t>
+  </si>
+  <si>
+    <t>2021Q4</t>
+  </si>
+  <si>
+    <t>1.-3. nóvember 2021</t>
+  </si>
+  <si>
+    <t>2022Q1</t>
+  </si>
+  <si>
+    <t>24.-26. janúar 2022</t>
+  </si>
+  <si>
+    <t>2022Q2</t>
+  </si>
+  <si>
+    <t>19.-22. apríl 2022</t>
+  </si>
+  <si>
+    <t>2022Q3</t>
+  </si>
+  <si>
+    <t>8.-10. ágúst 2022</t>
+  </si>
+  <si>
+    <t>2022Q4</t>
+  </si>
+  <si>
+    <t>7.-9. nóvember 2022</t>
+  </si>
+  <si>
+    <t>2023Q1</t>
+  </si>
+  <si>
+    <t>23.-25. janúar 2023</t>
+  </si>
+  <si>
+    <t>2023Q2</t>
+  </si>
+  <si>
+    <t>8.-10. maí 2023</t>
   </si>
   <si>
     <t>2023Q3</t>
@@ -705,19 +493,241 @@
     <t>5.-7. maí 2025</t>
   </si>
   <si>
-    <t>Birtingardagur / Date of publication: 14/5/2025</t>
-  </si>
-  <si>
     <t>2025Q3</t>
   </si>
   <si>
     <t>11.-13. ágúst 2025</t>
   </si>
   <si>
+    <t>2025Q4</t>
+  </si>
+  <si>
     <t>3. til 5. nóvember 2025</t>
   </si>
   <si>
-    <t>2025Q4</t>
+    <t>2026Q1</t>
+  </si>
+  <si>
+    <t>19. til 21. janúar 2026</t>
+  </si>
+  <si>
+    <t>Væntingakönnun markaðsaðila / Market expectations survey</t>
+  </si>
+  <si>
+    <t>Væntingar til skamms og meðallangs tíma / Short- and medium-term expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 1/ Question 1: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What do you think twelve-month inflation will measure, on average, in each quarter?</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Meðaltal / average</t>
+  </si>
+  <si>
+    <t>núverandi ársfjórðungur / current quarter</t>
+  </si>
+  <si>
+    <t>+1Q</t>
+  </si>
+  <si>
+    <t>+2Q</t>
+  </si>
+  <si>
+    <t>+3Q</t>
+  </si>
+  <si>
+    <t>+4Q</t>
+  </si>
+  <si>
+    <t>Miðgildi / median</t>
+  </si>
+  <si>
+    <t>Staðalfrávik / standard deviation</t>
+  </si>
+  <si>
+    <t>Heimild: Seðlabanki Íslands / Source: Central Bank of Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 2 / Question 2: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
+  </si>
+  <si>
+    <t>Meðaltal /average</t>
+  </si>
+  <si>
+    <t>Miðgildi /median</t>
+  </si>
+  <si>
+    <t>Staðalfrávik /standard deviation</t>
+  </si>
+  <si>
+    <t>Væntingar til skamms tíma / Short-term expectations</t>
+  </si>
+  <si>
+    <t>Spurning 3a / Question 3a:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á  stöðu ársverðbólgu eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Meðaltal / average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Miðgildi / median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Staðalfrávik / standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Hver er þín skoðun á gengi evru gagnvart krónu eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 12 months from now?</t>
+  </si>
+  <si>
+    <t>ISK/EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 3b / Question 3b: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu ársverðbólgu eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á gengi evru gagnvart krónu eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 3c / Question 3c: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 5 ár? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Hvað telur þú að skammtímanafnvextir verði að meðaltali næstu 5 ár? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að skammtímaraunvextir verði að meðaltali næstu 5 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t>Væntingar til langs tíma / Long-term expectations</t>
+  </si>
+  <si>
+    <t>Spurning 4 / Question 4:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 10 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að langtímanafnvextir verði að meðaltali næstu 10 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the long-term nominal interest rate be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að langtímaraunvextir verði að meðaltali næstu 10 ár? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the long-term real interest rate be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t>Álit á taumhalds peningastefnu Seðlabanka Íslands / Opinion of the Central Bank of Iceland‘s monetary stance</t>
+  </si>
+  <si>
+    <t>Spurning 5 / Question 5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What is your perception of the current monetary policy stance?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Alltof laust / far too loose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Of laust / too loose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Hæfilegt / appropriate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Of þétt /  too tight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Alltof þétt / far too tight</t>
   </si>
 </sst>
 </file>
@@ -725,14 +735,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,12 +1374,12 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1431,11 +1441,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1453,8 +1463,8 @@
     <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1481,6 +1491,9 @@
     <xf numFmtId="4" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="20% - Accent1" xfId="22" builtinId="30" customBuiltin="1"/>
@@ -1837,768 +1850,779 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:G78"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B1:G79"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="73" style="1" customWidth="1"/>
-    <col min="4" max="4" width="85.109375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="1"/>
+    <col min="4" max="4" width="85.140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:7">
       <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="19.2" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:7" ht="17.25">
       <c r="B6" s="14" t="s">
-        <v>194</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="15" customHeight="1">
       <c r="C8" s="13" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B9" s="9" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B10" s="9" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B11" s="9" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="B12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="15" customHeight="1">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="12" t="s">
+    <row r="14" spans="2:7" ht="15" customHeight="1"/>
+    <row r="15" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C15" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B16" s="9" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="B18" s="4"/>
       <c r="C18" s="3" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15" customHeight="1">
       <c r="B19" s="9" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15" customHeight="1"/>
+    <row r="22" spans="2:4">
       <c r="B22" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
       <c r="B23" s="9" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C23" s="10">
         <v>0.78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
       <c r="B24" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C24" s="10">
         <v>0.63</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
       <c r="B25" s="9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C25" s="10">
         <v>0.69</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
       <c r="B26" s="9" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C26" s="10">
         <v>0.64</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
       <c r="B27" s="9" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C27" s="10">
         <v>0.67</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
       <c r="B28" s="9" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C28" s="10">
         <v>0.69</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
       <c r="B29" s="9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10">
         <v>0.64</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
       <c r="B30" s="9" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C30" s="10">
         <v>0.56000000000000005</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
       <c r="B31" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C31" s="10">
         <v>0.59</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="B32" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C32" s="10">
         <v>0.74</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33" s="9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C33" s="10">
         <v>0.61</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
       <c r="B34" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C34" s="10">
         <v>0.68</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
       <c r="B35" s="9" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C35" s="10">
         <v>0.59</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
       <c r="B36" s="9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C36" s="10">
         <v>0.57999999999999996</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
       <c r="B37" s="9" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C37" s="10">
         <v>0.6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
       <c r="B38" s="9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C38" s="10">
         <v>0.45</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
       <c r="B39" s="9" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C39" s="10">
         <v>0.59</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
       <c r="B40" s="9" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C40" s="10">
         <v>0.41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
       <c r="B41" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C41" s="10">
         <v>0.66</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
       <c r="B42" s="9" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C42" s="10">
         <v>0.66</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
       <c r="B43" s="9" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C43" s="10">
         <v>0.56999999999999995</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
       <c r="B44" s="9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C44" s="10">
         <v>0.73</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
       <c r="B45" s="9" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C45" s="10">
         <v>0.6</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
       <c r="B46" s="9" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C46" s="10">
         <v>0.77</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
       <c r="B47" s="9" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C47" s="10">
         <v>0.83</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
       <c r="B48" s="9" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C48" s="10">
         <v>0.72</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
       <c r="B49" s="9" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C49" s="10">
         <v>0.7</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
       <c r="B50" s="9" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C50" s="10">
         <v>0.93</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
       <c r="B51" s="9" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C51" s="10">
         <v>0.75</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
       <c r="B52" s="9" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C52" s="10">
         <v>0.82</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
       <c r="B53" s="9" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C53" s="10">
         <v>0.86</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
       <c r="B54" s="9" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C54" s="10">
         <v>0.89</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
       <c r="B55" s="9" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C55" s="10">
         <v>0.86</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
       <c r="B56" s="9" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C56" s="10">
         <v>0.96</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
       <c r="B57" s="9" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C57" s="10">
         <v>0.86</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
       <c r="B58" s="9" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="C58" s="10">
         <v>0.9</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
       <c r="B59" s="9" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="C59" s="10">
         <v>0.9</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
       <c r="B60" s="9" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C60" s="10">
         <v>0.9</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
       <c r="B61" s="9" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C61" s="10">
         <v>0.83</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
       <c r="B62" s="9" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C62" s="10">
         <v>0.86206896551724133</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
       <c r="B63" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C63" s="10">
         <v>0.86</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
       <c r="B64" s="9" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="C64" s="10">
         <v>0.8</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
       <c r="B65" s="9" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C65" s="10">
         <v>0.77</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
       <c r="B66" s="9" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C66" s="10">
         <v>0.92</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
       <c r="B67" s="9" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="C67" s="10">
         <v>0.84</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
       <c r="B68" s="9" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="C68" s="10">
         <v>0.79</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
       <c r="B69" s="9" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="C69" s="10">
         <v>0.71</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
       <c r="B70" s="9" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="C70" s="10">
         <v>0.79</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
       <c r="B71" s="9" t="s">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="C71" s="10">
         <v>0.7</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
       <c r="B72" s="9" t="s">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="C72" s="10">
         <v>0.81</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
       <c r="B73" s="9" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="C73" s="10">
         <v>0.69</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
       <c r="B74" s="9" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="C74" s="10">
         <v>0.79</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
       <c r="B75" s="9" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="C75" s="10">
         <v>0.77</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
       <c r="B76" s="9" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="C76" s="10">
         <v>0.64102564102564108</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.4">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
       <c r="B77" s="9" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="C77" s="10">
         <v>0.76</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.4">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
       <c r="B78" s="9" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="C78" s="10">
         <v>0.78947368421052633</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>216</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2627,31 +2651,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:BE33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF33"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="8.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="1"/>
-    <col min="13" max="13" width="8.88671875" style="1" customWidth="1"/>
-    <col min="14" max="56" width="9.109375" style="1"/>
-    <col min="57" max="57" width="9.109375" style="11"/>
-    <col min="58" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="8.85546875" style="1" customWidth="1"/>
+    <col min="14" max="56" width="9.140625" style="1"/>
+    <col min="57" max="57" width="9.140625" style="11"/>
+    <col min="58" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -2661,15 +2685,15 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -2718,9 +2742,9 @@
       <c r="AT6" s="11"/>
       <c r="AU6" s="11"/>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2769,9 +2793,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2820,9 +2844,9 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -2881,10 +2905,10 @@
       <c r="BD9" s="22"/>
       <c r="BE9" s="22"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:58">
       <c r="A10" s="11"/>
       <c r="B10" s="8" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -2940,183 +2964,187 @@
       <c r="BB10" s="11"/>
       <c r="BC10" s="11"/>
       <c r="BD10" s="11"/>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="51"/>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q11" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="R11" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T11" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U11" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W11" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="P11" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q11" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R11" s="26" t="s">
+      <c r="Y11" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z11" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S11" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T11" s="26" t="s">
+      <c r="AA11" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U11" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V11" s="26" t="s">
+      <c r="AB11" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W11" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X11" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y11" s="26" t="s">
+      <c r="AC11" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD11" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE11" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF11" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG11" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI11" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ11" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK11" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL11" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM11" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN11" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO11" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP11" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ11" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR11" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS11" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z11" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA11" s="26" t="s">
+      <c r="AT11" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB11" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC11" s="26" t="s">
+      <c r="AU11" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD11" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE11" s="26" t="s">
+      <c r="AV11" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF11" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH11" s="26" t="s">
+      <c r="AW11" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX11" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI11" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ11" s="26" t="s">
+      <c r="AY11" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK11" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL11" s="26" t="s">
+      <c r="AZ11" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM11" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN11" s="26" t="s">
+      <c r="BA11" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO11" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP11" s="26" t="s">
+      <c r="BB11" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ11" s="26" t="s">
+      <c r="BC11" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD11" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR11" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS11" s="26" t="s">
+      <c r="BE11" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="AT11" s="26" t="s">
+      <c r="BF11" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="AU11" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV11" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW11" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX11" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY11" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ11" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA11" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB11" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC11" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD11" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE11" s="26" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B12" s="29">
         <v>5.89</v>
@@ -3286,10 +3314,13 @@
       <c r="BE12" s="34">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B13" s="29">
         <v>5.17</v>
@@ -3459,10 +3490,13 @@
       <c r="BE13" s="34">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B14" s="29">
         <v>5.07</v>
@@ -3632,10 +3666,13 @@
       <c r="BE14" s="34">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="34">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B15" s="24">
         <v>4.95</v>
@@ -3805,10 +3842,13 @@
       <c r="BE15" s="34">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="34">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B16" s="29">
         <v>4.71</v>
@@ -3976,10 +4016,13 @@
         <v>3.3</v>
       </c>
       <c r="BE16" s="34">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+        <v>3.4</v>
+      </c>
+      <c r="BF16" s="34">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="37"/>
       <c r="B17" s="29"/>
       <c r="C17" s="11"/>
@@ -4037,183 +4080,187 @@
       <c r="BC17" s="11"/>
       <c r="BD17" s="11"/>
       <c r="BE17" s="34"/>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34"/>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="26" t="s">
+      <c r="H18" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="26" t="s">
+      <c r="M18" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="26" t="s">
+      <c r="O18" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="26" t="s">
+      <c r="Q18" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N18" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O18" s="26" t="s">
+      <c r="R18" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S18" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T18" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U18" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P18" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q18" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R18" s="26" t="s">
+      <c r="V18" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W18" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X18" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y18" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z18" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T18" s="26" t="s">
+      <c r="AA18" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U18" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V18" s="26" t="s">
+      <c r="AB18" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W18" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X18" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y18" s="26" t="s">
+      <c r="AC18" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD18" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE18" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF18" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG18" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH18" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI18" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ18" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK18" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL18" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM18" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN18" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO18" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP18" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR18" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS18" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z18" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA18" s="26" t="s">
+      <c r="AT18" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB18" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC18" s="26" t="s">
+      <c r="AU18" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD18" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE18" s="26" t="s">
+      <c r="AV18" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF18" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG18" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH18" s="26" t="s">
+      <c r="AW18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX18" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI18" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ18" s="26" t="s">
+      <c r="AY18" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK18" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL18" s="26" t="s">
+      <c r="AZ18" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM18" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN18" s="26" t="s">
+      <c r="BA18" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO18" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP18" s="26" t="s">
+      <c r="BB18" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ18" s="26" t="s">
+      <c r="BC18" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD18" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR18" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS18" s="26" t="s">
+      <c r="BE18" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="AT18" s="26" t="s">
+      <c r="BF18" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="AU18" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV18" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW18" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX18" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY18" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ18" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA18" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB18" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC18" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD18" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE18" s="44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B19" s="24">
         <v>6.15</v>
@@ -4383,10 +4430,13 @@
       <c r="BE19" s="34">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="34">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B20" s="29">
         <v>5.5</v>
@@ -4556,10 +4606,13 @@
       <c r="BE20" s="34">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="34">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B21" s="29">
         <v>5.0999999999999996</v>
@@ -4729,10 +4782,13 @@
       <c r="BE21" s="34">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="34">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B22" s="24">
         <v>5.15</v>
@@ -4902,10 +4958,13 @@
       <c r="BE22" s="34">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="34">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B23" s="24">
         <v>4.8499999999999996</v>
@@ -5075,8 +5134,11 @@
       <c r="BE23" s="34">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="37"/>
       <c r="B24" s="29"/>
       <c r="C24" s="11"/>
@@ -5134,183 +5196,187 @@
       <c r="BC24" s="11"/>
       <c r="BD24" s="11"/>
       <c r="BE24" s="34"/>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34"/>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="O25" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P25" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q25" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="R25" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S25" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T25" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U25" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="V25" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W25" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X25" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y25" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M25" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="N25" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O25" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="P25" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q25" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R25" s="26" t="s">
+      <c r="Z25" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S25" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T25" s="26" t="s">
+      <c r="AA25" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U25" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V25" s="26" t="s">
+      <c r="AB25" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W25" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X25" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y25" s="26" t="s">
+      <c r="AC25" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD25" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE25" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF25" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG25" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH25" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI25" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ25" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK25" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL25" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM25" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN25" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO25" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP25" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ25" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR25" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS25" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z25" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA25" s="26" t="s">
+      <c r="AT25" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB25" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC25" s="26" t="s">
+      <c r="AU25" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD25" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE25" s="26" t="s">
+      <c r="AV25" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF25" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG25" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH25" s="26" t="s">
+      <c r="AW25" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX25" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI25" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ25" s="26" t="s">
+      <c r="AY25" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK25" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL25" s="26" t="s">
+      <c r="AZ25" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM25" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN25" s="26" t="s">
+      <c r="BA25" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO25" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP25" s="26" t="s">
+      <c r="BB25" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ25" s="26" t="s">
+      <c r="BC25" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD25" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR25" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS25" s="26" t="s">
+      <c r="BE25" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="AT25" s="26" t="s">
+      <c r="BF25" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="AU25" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV25" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW25" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX25" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY25" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ25" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA25" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB25" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC25" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD25" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE25" s="44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B26" s="29">
         <v>1.01</v>
@@ -5478,12 +5544,15 @@
         <v>0.1</v>
       </c>
       <c r="BE26" s="34">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="BF26" s="34">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B27" s="29">
         <v>1.24</v>
@@ -5653,10 +5722,13 @@
       <c r="BE27" s="34">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF27" s="34">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:58">
       <c r="A28" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B28" s="29">
         <v>1.19</v>
@@ -5826,10 +5898,13 @@
       <c r="BE28" s="34">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF28" s="34">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58">
       <c r="A29" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B29" s="29">
         <v>1.34</v>
@@ -5997,12 +6072,15 @@
         <v>0.25</v>
       </c>
       <c r="BE29" s="34">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="BF29" s="34">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
       <c r="A30" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B30" s="29">
         <v>1.1399999999999999</v>
@@ -6170,10 +6248,13 @@
         <v>0.3</v>
       </c>
       <c r="BE30" s="34">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0.30130000000000001</v>
+      </c>
+      <c r="BF30" s="34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -6232,9 +6313,9 @@
       <c r="BD31" s="22"/>
       <c r="BE31" s="22"/>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:58">
       <c r="A32" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6286,8 +6367,9 @@
       <c r="AW32" s="11"/>
       <c r="AX32" s="11"/>
       <c r="AY32" s="11"/>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="BF32" s="51"/>
+    </row>
+    <row r="33" spans="1:48">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6347,42 +6429,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:BE33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF33"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="8.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="1"/>
-    <col min="13" max="13" width="8.88671875" style="1" customWidth="1"/>
-    <col min="14" max="56" width="9.109375" style="1"/>
-    <col min="57" max="57" width="8.109375" style="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="8.85546875" style="1" customWidth="1"/>
+    <col min="14" max="56" width="9.140625" style="1"/>
+    <col min="57" max="57" width="8.140625" style="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -6431,9 +6513,9 @@
       <c r="AT6" s="11"/>
       <c r="AU6" s="11"/>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -6482,9 +6564,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -6533,9 +6615,9 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -6590,10 +6672,10 @@
       <c r="AZ9" s="22"/>
       <c r="BA9" s="22"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:58">
       <c r="A10" s="42"/>
       <c r="B10" s="43" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -6650,183 +6732,187 @@
       <c r="BC10" s="42"/>
       <c r="BD10" s="42"/>
       <c r="BE10" s="42"/>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="51"/>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="26" t="s">
+      <c r="H11" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="26" t="s">
+      <c r="M11" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="35" t="s">
+      <c r="O11" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="35" t="s">
+      <c r="Q11" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="N11" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="35" t="s">
+      <c r="R11" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="U11" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="P11" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q11" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="R11" s="35" t="s">
+      <c r="V11" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="W11" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y11" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z11" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="S11" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="T11" s="35" t="s">
+      <c r="AA11" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="U11" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="V11" s="35" t="s">
+      <c r="AB11" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="W11" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="X11" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y11" s="35" t="s">
+      <c r="AC11" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD11" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE11" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF11" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG11" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI11" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ11" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK11" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL11" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM11" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN11" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO11" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP11" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ11" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR11" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS11" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z11" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA11" s="35" t="s">
+      <c r="AT11" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB11" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC11" s="35" t="s">
+      <c r="AU11" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD11" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE11" s="26" t="s">
+      <c r="AV11" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF11" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH11" s="26" t="s">
+      <c r="AW11" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX11" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI11" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ11" s="26" t="s">
+      <c r="AY11" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK11" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL11" s="26" t="s">
+      <c r="AZ11" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM11" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN11" s="26" t="s">
+      <c r="BA11" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO11" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP11" s="26" t="s">
+      <c r="BB11" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ11" s="26" t="s">
+      <c r="BC11" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD11" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR11" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS11" s="26" t="s">
+      <c r="BE11" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AT11" s="26" t="s">
+      <c r="BF11" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="AU11" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV11" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW11" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX11" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY11" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ11" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA11" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB11" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC11" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD11" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE11" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B12" s="29">
         <v>4.91</v>
@@ -6996,10 +7082,13 @@
       <c r="BE12" s="48">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B13" s="29">
         <v>5.1100000000000003</v>
@@ -7169,10 +7258,13 @@
       <c r="BE13" s="48">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B14" s="29">
         <v>5.38</v>
@@ -7342,10 +7434,13 @@
       <c r="BE14" s="48">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="34">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B15" s="29">
         <v>5.53</v>
@@ -7515,10 +7610,13 @@
       <c r="BE15" s="48">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="34">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B16" s="29">
         <v>5.73</v>
@@ -7688,8 +7786,11 @@
       <c r="BE16" s="48">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF16" s="34">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="37"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7747,183 +7848,187 @@
       <c r="BC17" s="11"/>
       <c r="BD17" s="11"/>
       <c r="BE17" s="49"/>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34"/>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="F18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="26" t="s">
+      <c r="H18" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="26" t="s">
+      <c r="M18" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="35" t="s">
+      <c r="O18" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="35" t="s">
+      <c r="Q18" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="N18" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="O18" s="35" t="s">
+      <c r="R18" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="S18" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="T18" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="U18" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="P18" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q18" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="R18" s="35" t="s">
+      <c r="V18" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="W18" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="X18" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y18" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z18" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="S18" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="T18" s="35" t="s">
+      <c r="AA18" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="U18" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="V18" s="35" t="s">
+      <c r="AB18" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="W18" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="X18" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y18" s="35" t="s">
+      <c r="AC18" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD18" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE18" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF18" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG18" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH18" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI18" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ18" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK18" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL18" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM18" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN18" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO18" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP18" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR18" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS18" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z18" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA18" s="35" t="s">
+      <c r="AT18" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB18" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC18" s="35" t="s">
+      <c r="AU18" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD18" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE18" s="26" t="s">
+      <c r="AV18" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF18" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG18" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH18" s="26" t="s">
+      <c r="AW18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX18" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI18" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ18" s="26" t="s">
+      <c r="AY18" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK18" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL18" s="26" t="s">
+      <c r="AZ18" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM18" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN18" s="26" t="s">
+      <c r="BA18" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO18" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP18" s="26" t="s">
+      <c r="BB18" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ18" s="26" t="s">
+      <c r="BC18" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD18" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR18" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS18" s="26" t="s">
+      <c r="BE18" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AT18" s="26" t="s">
+      <c r="BF18" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="AU18" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV18" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW18" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX18" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY18" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ18" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA18" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB18" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC18" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD18" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE18" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B19" s="29">
         <v>5</v>
@@ -8093,10 +8198,13 @@
       <c r="BE19" s="49">
         <v>8.25</v>
       </c>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B20" s="29">
         <v>5</v>
@@ -8266,10 +8374,13 @@
       <c r="BE20" s="49">
         <v>7.75</v>
       </c>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="34">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B21" s="24">
         <v>5.25</v>
@@ -8439,10 +8550,13 @@
       <c r="BE21" s="49">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="34">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B22" s="29">
         <v>5.37</v>
@@ -8612,10 +8726,13 @@
       <c r="BE22" s="49">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="34">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B23" s="24">
         <v>5.75</v>
@@ -8785,8 +8902,11 @@
       <c r="BE23" s="48">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="37"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8844,183 +8964,187 @@
       <c r="BC24" s="11"/>
       <c r="BD24" s="11"/>
       <c r="BE24" s="49"/>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34"/>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="11" t="s">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C25" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="26" t="s">
+      <c r="H25" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="26" t="s">
+      <c r="M25" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="J25" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K25" s="35" t="s">
+      <c r="O25" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="P25" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="L25" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="M25" s="35" t="s">
+      <c r="Q25" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="N25" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="O25" s="35" t="s">
+      <c r="R25" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="S25" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="T25" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="U25" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="P25" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q25" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="R25" s="35" t="s">
+      <c r="V25" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="W25" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="X25" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y25" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z25" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="S25" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="T25" s="35" t="s">
+      <c r="AA25" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="U25" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="V25" s="35" t="s">
+      <c r="AB25" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="W25" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="X25" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y25" s="35" t="s">
+      <c r="AC25" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD25" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE25" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF25" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG25" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH25" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI25" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ25" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK25" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL25" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM25" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN25" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO25" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP25" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ25" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR25" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS25" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z25" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA25" s="35" t="s">
+      <c r="AT25" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB25" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC25" s="35" t="s">
+      <c r="AU25" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD25" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE25" s="26" t="s">
+      <c r="AV25" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF25" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG25" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH25" s="26" t="s">
+      <c r="AW25" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX25" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI25" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ25" s="26" t="s">
+      <c r="AY25" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK25" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL25" s="26" t="s">
+      <c r="AZ25" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM25" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN25" s="26" t="s">
+      <c r="BA25" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO25" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP25" s="26" t="s">
+      <c r="BB25" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ25" s="26" t="s">
+      <c r="BC25" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD25" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR25" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS25" s="26" t="s">
+      <c r="BE25" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="AT25" s="26" t="s">
+      <c r="BF25" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="AU25" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV25" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW25" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX25" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY25" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ25" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA25" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB25" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC25" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD25" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE25" s="50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="B26" s="29">
         <v>0.16</v>
@@ -9190,10 +9314,13 @@
       <c r="BE26" s="48">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF26" s="34">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="37" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B27" s="29">
         <v>0.27</v>
@@ -9363,10 +9490,13 @@
       <c r="BE27" s="48">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF27" s="34">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:58">
       <c r="A28" s="37" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B28" s="29">
         <v>0.46</v>
@@ -9536,10 +9666,13 @@
       <c r="BE28" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF28" s="34">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58">
       <c r="A29" s="37" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="B29" s="29">
         <v>0.68</v>
@@ -9709,10 +9842,13 @@
       <c r="BE29" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF29" s="34">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
       <c r="A30" s="37" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B30" s="29">
         <v>0.76</v>
@@ -9882,8 +10018,11 @@
       <c r="BE30" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF30" s="34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -9942,9 +10081,9 @@
       <c r="BD31" s="22"/>
       <c r="BE31" s="27"/>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:58">
       <c r="A32" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -9997,8 +10136,9 @@
       <c r="AX32" s="11"/>
       <c r="AY32" s="11"/>
       <c r="AZ32" s="11"/>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.4">
+      <c r="BF32" s="51"/>
+    </row>
+    <row r="33" spans="1:47">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10059,205 +10199,208 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE39"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF39"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="26" t="s">
+      <c r="M6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="26" t="s">
+      <c r="O6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="26" t="s">
+      <c r="Q6" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="26" t="s">
+      <c r="R6" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R6" s="26" t="s">
+      <c r="V6" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S6" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="26" t="s">
+      <c r="AA6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U6" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="26" t="s">
+      <c r="AB6" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X6" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="26" t="s">
+      <c r="AC6" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ6" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS6" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA6" s="26" t="s">
+      <c r="AT6" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB6" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC6" s="26" t="s">
+      <c r="AU6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD6" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE6" s="26" t="s">
+      <c r="AV6" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF6" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH6" s="26" t="s">
+      <c r="AW6" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="26" t="s">
+      <c r="AY6" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK6" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL6" s="26" t="s">
+      <c r="AZ6" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM6" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN6" s="26" t="s">
+      <c r="BA6" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP6" s="26" t="s">
+      <c r="BB6" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ6" s="26" t="s">
+      <c r="BC6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD6" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS6" s="26" t="s">
+      <c r="BE6" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="AT6" s="26" t="s">
+      <c r="BF6" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="AU6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV6" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW6" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX6" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY6" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ6" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB6" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC6" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD6" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE6" s="50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10316,9 +10459,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -10377,12 +10520,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>11</v>
+        <v>171</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
@@ -10440,9 +10583,9 @@
       <c r="BD9" s="33"/>
       <c r="BE9" s="33"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:58">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B10" s="34">
         <v>4.99</v>
@@ -10612,10 +10755,13 @@
       <c r="BE10" s="48">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="52">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B11" s="34">
         <v>5</v>
@@ -10785,10 +10931,13 @@
       <c r="BE11" s="48">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF11" s="34">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B12" s="34">
         <v>0.84</v>
@@ -10958,8 +11107,11 @@
       <c r="BE12" s="48">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -11017,10 +11169,11 @@
       <c r="BC13" s="11"/>
       <c r="BD13" s="11"/>
       <c r="BE13" s="48"/>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34"/>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="11" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -11078,13 +11231,14 @@
       <c r="BC14" s="11"/>
       <c r="BD14" s="11"/>
       <c r="BE14" s="48"/>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="34"/>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="22" t="s">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
@@ -11141,10 +11295,11 @@
       <c r="BC15" s="33"/>
       <c r="BD15" s="33"/>
       <c r="BE15" s="33"/>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="34"/>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B16" s="34">
         <v>164.72</v>
@@ -11314,10 +11469,13 @@
       <c r="BE16" s="48">
         <v>149.69999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF16" s="52">
+        <v>148.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B17" s="34">
         <v>165</v>
@@ -11487,10 +11645,13 @@
       <c r="BE17" s="48">
         <v>149</v>
       </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B18" s="34">
         <v>5.65</v>
@@ -11660,8 +11821,11 @@
       <c r="BE18" s="48">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF18" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -11719,10 +11883,11 @@
       <c r="BC19" s="34"/>
       <c r="BD19" s="34"/>
       <c r="BE19" s="48"/>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="34"/>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="11" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -11780,13 +11945,14 @@
       <c r="BC20" s="34"/>
       <c r="BD20" s="34"/>
       <c r="BE20" s="48"/>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="34"/>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="22" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C21" s="33"/>
       <c r="D21" s="33"/>
@@ -11843,10 +12009,11 @@
       <c r="BC21" s="33"/>
       <c r="BD21" s="33"/>
       <c r="BE21" s="33"/>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="34"/>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B22" s="34">
         <v>5.73</v>
@@ -12016,10 +12183,13 @@
       <c r="BE22" s="48">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B23" s="34">
         <v>5.5</v>
@@ -12189,10 +12359,13 @@
       <c r="BE23" s="48">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B24" s="34">
         <v>1.02</v>
@@ -12362,8 +12535,11 @@
       <c r="BE24" s="48">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -12421,10 +12597,11 @@
       <c r="BC25" s="11"/>
       <c r="BD25" s="11"/>
       <c r="BE25" s="48"/>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF25" s="34"/>
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="11" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -12473,13 +12650,14 @@
       <c r="AT26" s="11"/>
       <c r="AU26" s="11"/>
       <c r="BE26" s="48"/>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF26" s="34"/>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="22" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="33"/>
@@ -12536,10 +12714,11 @@
       <c r="BC27" s="33"/>
       <c r="BD27" s="33"/>
       <c r="BE27" s="33"/>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF27" s="34"/>
+    </row>
+    <row r="28" spans="1:58">
       <c r="A28" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -12685,10 +12864,13 @@
       <c r="BE28" s="48">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF28" s="52">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58">
       <c r="A29" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -12834,10 +13016,13 @@
       <c r="BE29" s="48">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF29" s="34">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
       <c r="A30" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -12983,8 +13168,11 @@
       <c r="BE30" s="48">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF30" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58">
       <c r="A31" s="11"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -13042,10 +13230,11 @@
       <c r="BC31" s="34"/>
       <c r="BD31" s="34"/>
       <c r="BE31" s="49"/>
-    </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF31" s="34"/>
+    </row>
+    <row r="32" spans="1:58">
       <c r="A32" s="11" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -13103,13 +13292,14 @@
       <c r="BC32" s="34"/>
       <c r="BD32" s="34"/>
       <c r="BE32" s="49"/>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF32" s="34"/>
+    </row>
+    <row r="33" spans="1:58">
       <c r="A33" s="22" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
@@ -13166,10 +13356,11 @@
       <c r="BC33" s="33"/>
       <c r="BD33" s="33"/>
       <c r="BE33" s="33"/>
-    </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF33" s="34"/>
+    </row>
+    <row r="34" spans="1:58">
       <c r="A34" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -13315,10 +13506,13 @@
       <c r="BE34" s="48">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF34" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:58">
       <c r="A35" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -13464,10 +13658,13 @@
       <c r="BE35" s="48">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF35" s="34">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:58">
       <c r="A36" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -13613,8 +13810,11 @@
       <c r="BE36" s="48">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF36" s="34">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:58">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -13672,8 +13872,9 @@
       <c r="BC37" s="22"/>
       <c r="BD37" s="22"/>
       <c r="BE37" s="22"/>
-    </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF37" s="34"/>
+    </row>
+    <row r="38" spans="1:58">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -13730,10 +13931,11 @@
       <c r="BB38" s="11"/>
       <c r="BC38" s="11"/>
       <c r="BD38" s="11"/>
-    </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF38" s="51"/>
+    </row>
+    <row r="39" spans="1:58">
       <c r="A39" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -13794,210 +13996,213 @@
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE40"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF40"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58">
       <c r="A2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="26" t="s">
+      <c r="M6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="26" t="s">
+      <c r="O6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="26" t="s">
+      <c r="Q6" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="26" t="s">
+      <c r="R6" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R6" s="26" t="s">
+      <c r="V6" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S6" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="26" t="s">
+      <c r="AA6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U6" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="26" t="s">
+      <c r="AB6" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X6" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="26" t="s">
+      <c r="AC6" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ6" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS6" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA6" s="26" t="s">
+      <c r="AT6" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB6" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC6" s="26" t="s">
+      <c r="AU6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD6" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE6" s="26" t="s">
+      <c r="AV6" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF6" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH6" s="26" t="s">
+      <c r="AW6" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="26" t="s">
+      <c r="AY6" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK6" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL6" s="26" t="s">
+      <c r="AZ6" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM6" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN6" s="26" t="s">
+      <c r="BA6" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP6" s="26" t="s">
+      <c r="BB6" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ6" s="26" t="s">
+      <c r="BC6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD6" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS6" s="26" t="s">
+      <c r="BE6" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AT6" s="26" t="s">
+      <c r="BF6" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AU6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV6" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW6" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX6" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY6" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ6" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB6" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC6" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD6" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE6" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -14056,9 +14261,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -14117,12 +14322,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
@@ -14180,9 +14385,9 @@
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:58">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B10" s="24">
         <v>4.68</v>
@@ -14352,10 +14557,13 @@
       <c r="BE10" s="48">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="52">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B11" s="24">
         <v>5</v>
@@ -14525,10 +14733,13 @@
       <c r="BE11" s="48">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF11" s="34">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B12" s="24">
         <v>0.89</v>
@@ -14698,8 +14909,11 @@
       <c r="BE12" s="48">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>0.39989999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="11"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -14757,10 +14971,11 @@
       <c r="BC13" s="24"/>
       <c r="BD13" s="24"/>
       <c r="BE13" s="49"/>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34"/>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="11" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -14818,13 +15033,14 @@
       <c r="BC14" s="24"/>
       <c r="BD14" s="24"/>
       <c r="BE14" s="49"/>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="34"/>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="22" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
@@ -14881,10 +15097,11 @@
       <c r="BC15" s="28"/>
       <c r="BD15" s="28"/>
       <c r="BE15" s="28"/>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="34"/>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B16" s="24">
         <v>167.65</v>
@@ -15054,10 +15271,13 @@
       <c r="BE16" s="48">
         <v>150.80000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF16" s="52">
+        <v>149.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B17" s="24">
         <v>168.5</v>
@@ -15227,10 +15447,13 @@
       <c r="BE17" s="48">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B18" s="24">
         <v>10.94</v>
@@ -15400,8 +15623,11 @@
       <c r="BE18" s="48">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF18" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11"/>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -15459,10 +15685,11 @@
       <c r="BC19" s="24"/>
       <c r="BD19" s="24"/>
       <c r="BE19" s="49"/>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="34"/>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="11" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -15520,13 +15747,14 @@
       <c r="BC20" s="24"/>
       <c r="BD20" s="24"/>
       <c r="BE20" s="49"/>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="34"/>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="22" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -15583,10 +15811,11 @@
       <c r="BC21" s="28"/>
       <c r="BD21" s="28"/>
       <c r="BE21" s="28"/>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="34"/>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B22" s="24">
         <v>6.41</v>
@@ -15756,10 +15985,13 @@
       <c r="BE22" s="48">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="52">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B23" s="24">
         <v>6.13</v>
@@ -15929,10 +16161,13 @@
       <c r="BE23" s="48">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B24" s="24">
         <v>1.34</v>
@@ -16102,8 +16337,11 @@
       <c r="BE24" s="48">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -16161,10 +16399,11 @@
       <c r="BC25" s="11"/>
       <c r="BD25" s="11"/>
       <c r="BE25" s="49"/>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF25" s="34"/>
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="11" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -16222,13 +16461,14 @@
       <c r="BC26" s="11"/>
       <c r="BD26" s="11"/>
       <c r="BE26" s="49"/>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF26" s="34"/>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="22" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
@@ -16242,7 +16482,7 @@
       <c r="L27" s="28"/>
       <c r="M27" s="28"/>
       <c r="N27" s="28" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="O27" s="28"/>
       <c r="P27" s="28"/>
@@ -16287,10 +16527,11 @@
       <c r="BC27" s="28"/>
       <c r="BD27" s="28"/>
       <c r="BE27" s="28"/>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF27" s="34"/>
+    </row>
+    <row r="28" spans="1:58">
       <c r="A28" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -16436,10 +16677,13 @@
       <c r="BE28" s="48">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF28" s="52">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58">
       <c r="A29" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -16585,10 +16829,13 @@
       <c r="BE29" s="48">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF29" s="34">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
       <c r="A30" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -16734,8 +16981,11 @@
       <c r="BE30" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF30" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58">
       <c r="A31" s="11"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
@@ -16793,10 +17043,11 @@
       <c r="BC31" s="24"/>
       <c r="BD31" s="24"/>
       <c r="BE31" s="49"/>
-    </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF31" s="34"/>
+    </row>
+    <row r="32" spans="1:58">
       <c r="A32" s="11" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -16854,13 +17105,14 @@
       <c r="BC32" s="24"/>
       <c r="BD32" s="24"/>
       <c r="BE32" s="49"/>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF32" s="34"/>
+    </row>
+    <row r="33" spans="1:58">
       <c r="A33" s="22" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -16917,10 +17169,11 @@
       <c r="BC33" s="28"/>
       <c r="BD33" s="28"/>
       <c r="BE33" s="28"/>
-    </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF33" s="34"/>
+    </row>
+    <row r="34" spans="1:58">
       <c r="A34" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
@@ -17066,10 +17319,13 @@
       <c r="BE34" s="48">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF34" s="52">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:58">
       <c r="A35" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
@@ -17215,10 +17471,13 @@
       <c r="BE35" s="48">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF35" s="34">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:58">
       <c r="A36" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -17364,8 +17623,11 @@
       <c r="BE36" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF36" s="34">
+        <v>0.75249999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:58">
       <c r="A37" s="22"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -17424,7 +17686,7 @@
       <c r="BD37" s="28"/>
       <c r="BE37" s="28"/>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:58">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -17474,10 +17736,11 @@
       <c r="AU38" s="11"/>
       <c r="AV38" s="11"/>
       <c r="AW38" s="11"/>
-    </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF38" s="51"/>
+    </row>
+    <row r="39" spans="1:58">
       <c r="A39" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -17528,7 +17791,7 @@
       <c r="AV39" s="11"/>
       <c r="AW39" s="11"/>
     </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:58">
       <c r="A40" s="32"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -17591,207 +17854,210 @@
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE28"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="15" width="11.44140625" style="1" customWidth="1"/>
-    <col min="16" max="18" width="9.6640625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="15" width="11.42578125" style="1" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="26" t="s">
+      <c r="M6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="26" t="s">
+      <c r="O6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="26" t="s">
+      <c r="Q6" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="26" t="s">
+      <c r="R6" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R6" s="26" t="s">
+      <c r="V6" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S6" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="26" t="s">
+      <c r="AA6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U6" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="26" t="s">
+      <c r="AB6" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X6" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="26" t="s">
+      <c r="AC6" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ6" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS6" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA6" s="26" t="s">
+      <c r="AT6" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB6" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC6" s="26" t="s">
+      <c r="AU6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD6" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE6" s="26" t="s">
+      <c r="AV6" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF6" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH6" s="26" t="s">
+      <c r="AW6" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="26" t="s">
+      <c r="AY6" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK6" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL6" s="26" t="s">
+      <c r="AZ6" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM6" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN6" s="26" t="s">
+      <c r="BA6" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP6" s="26" t="s">
+      <c r="BB6" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ6" s="26" t="s">
+      <c r="BC6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD6" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS6" s="26" t="s">
+      <c r="BE6" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AT6" s="26" t="s">
+      <c r="BF6" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AU6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV6" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW6" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX6" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY6" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ6" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB6" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC6" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD6" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE6" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -17850,9 +18116,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -17911,12 +18177,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -17973,10 +18239,11 @@
       <c r="BC9" s="28"/>
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
-    </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF9" s="53"/>
+    </row>
+    <row r="10" spans="1:58">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B10" s="24">
         <v>4.55</v>
@@ -18146,10 +18413,13 @@
       <c r="BE10" s="48">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="52">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B11" s="29">
         <v>4.8</v>
@@ -18319,10 +18589,13 @@
       <c r="BE11" s="48">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF11" s="34">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B12" s="24">
         <v>0.85</v>
@@ -18492,8 +18765,11 @@
       <c r="BE12" s="48">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="11"/>
       <c r="B13" s="24"/>
       <c r="C13" s="29"/>
@@ -18551,10 +18827,11 @@
       <c r="BC13" s="11"/>
       <c r="BD13" s="11"/>
       <c r="BE13" s="48"/>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34"/>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="11" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -18612,13 +18889,14 @@
       <c r="BC14" s="11"/>
       <c r="BD14" s="11"/>
       <c r="BE14" s="49"/>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="11"/>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="22" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -18675,10 +18953,11 @@
       <c r="BC15" s="28"/>
       <c r="BD15" s="28"/>
       <c r="BE15" s="28"/>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="24"/>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -18824,10 +19103,13 @@
       <c r="BE16" s="48">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF16" s="52">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -18973,10 +19255,13 @@
       <c r="BE17" s="48">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
@@ -19122,8 +19407,11 @@
       <c r="BE18" s="48">
         <v>0.55000000000000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF18" s="34">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -19181,10 +19469,11 @@
       <c r="BC19" s="24"/>
       <c r="BD19" s="24"/>
       <c r="BE19" s="49"/>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="11"/>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="11" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19242,13 +19531,14 @@
       <c r="BC20" s="24"/>
       <c r="BD20" s="24"/>
       <c r="BE20" s="49"/>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="11"/>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="22" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
@@ -19305,10 +19595,11 @@
       <c r="BC21" s="28"/>
       <c r="BD21" s="28"/>
       <c r="BE21" s="28"/>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="24"/>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -19454,10 +19745,13 @@
       <c r="BE22" s="48">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="52">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -19603,10 +19897,13 @@
       <c r="BE23" s="48">
         <v>2.95</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="29"/>
@@ -19752,8 +20049,11 @@
       <c r="BE24" s="48">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -19811,8 +20111,9 @@
       <c r="BC25" s="28"/>
       <c r="BD25" s="28"/>
       <c r="BE25" s="28"/>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF25" s="24"/>
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -19862,10 +20163,11 @@
       <c r="AU26" s="11"/>
       <c r="AV26" s="11"/>
       <c r="AW26" s="11"/>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF26" s="51"/>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -19915,7 +20217,7 @@
       <c r="AU27" s="11"/>
       <c r="AV27" s="11"/>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:58">
       <c r="A28" s="6"/>
     </row>
   </sheetData>
@@ -19930,207 +20232,210 @@
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE27"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BF27"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="15" width="11.88671875" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.5546875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="15" width="11.85546875" style="1" customWidth="1"/>
+    <col min="16" max="18" width="10.5703125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:58">
       <c r="A5" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="26" t="s">
+      <c r="M6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="26" t="s">
+      <c r="O6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="26" t="s">
+      <c r="Q6" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="26" t="s">
+      <c r="R6" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R6" s="26" t="s">
+      <c r="V6" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="S6" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="26" t="s">
+      <c r="AA6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="U6" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="26" t="s">
+      <c r="AB6" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="X6" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="26" t="s">
+      <c r="AC6" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ6" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS6" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA6" s="26" t="s">
+      <c r="AT6" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="AB6" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC6" s="26" t="s">
+      <c r="AU6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AD6" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE6" s="26" t="s">
+      <c r="AV6" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AF6" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AH6" s="26" t="s">
+      <c r="AW6" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AI6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="26" t="s">
+      <c r="AY6" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AK6" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL6" s="26" t="s">
+      <c r="AZ6" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="AM6" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN6" s="26" t="s">
+      <c r="BA6" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AO6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP6" s="26" t="s">
+      <c r="BB6" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="AQ6" s="26" t="s">
+      <c r="BC6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD6" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS6" s="26" t="s">
+      <c r="BE6" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AT6" s="26" t="s">
+      <c r="BF6" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AU6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV6" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW6" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX6" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY6" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ6" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB6" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC6" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="BD6" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="BE6" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:58">
       <c r="A7" s="21" t="s">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -20189,9 +20494,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="46"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:58">
       <c r="A8" s="11" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -20250,12 +20555,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="46"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:58">
       <c r="A9" s="22" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -20313,9 +20618,9 @@
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:58">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B10" s="29">
         <v>4.32</v>
@@ -20485,10 +20790,13 @@
       <c r="BE10" s="45">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF10" s="52">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B11" s="29">
         <v>4.5</v>
@@ -20658,10 +20966,13 @@
       <c r="BE11" s="45">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF11" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B12" s="29">
         <v>0.82</v>
@@ -20831,8 +21142,11 @@
       <c r="BE12" s="45">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF12" s="34">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -20890,10 +21204,11 @@
       <c r="BC13" s="24"/>
       <c r="BD13" s="24"/>
       <c r="BE13" s="46"/>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF13" s="34"/>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="11" t="s">
-        <v>115</v>
+        <v>207</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -20951,13 +21266,14 @@
       <c r="BC14" s="24"/>
       <c r="BD14" s="24"/>
       <c r="BE14" s="46"/>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF14" s="34"/>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="22" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -21014,10 +21330,11 @@
       <c r="BC15" s="28"/>
       <c r="BD15" s="28"/>
       <c r="BE15" s="28"/>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF15" s="34"/>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B16" s="29">
         <v>7.02</v>
@@ -21187,10 +21504,13 @@
       <c r="BE16" s="45">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF16" s="52">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B17" s="29">
         <v>7.05</v>
@@ -21360,10 +21680,13 @@
       <c r="BE17" s="45">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF17" s="34">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B18" s="29">
         <v>1.03</v>
@@ -21533,8 +21856,11 @@
       <c r="BE18" s="45">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF18" s="34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -21592,10 +21918,11 @@
       <c r="BC19" s="24"/>
       <c r="BD19" s="24"/>
       <c r="BE19" s="46"/>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF19" s="34"/>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="11" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -21653,13 +21980,14 @@
       <c r="BC20" s="24"/>
       <c r="BD20" s="24"/>
       <c r="BE20" s="46"/>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF20" s="34"/>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="22" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
@@ -21716,10 +22044,11 @@
       <c r="BC21" s="28"/>
       <c r="BD21" s="28"/>
       <c r="BE21" s="28"/>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF21" s="34"/>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B22" s="29">
         <v>2.23</v>
@@ -21889,10 +22218,13 @@
       <c r="BE22" s="45">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF22" s="52">
+        <v>2.5032999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="B23" s="29">
         <v>2.37</v>
@@ -22062,10 +22394,13 @@
       <c r="BE23" s="45">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF23" s="34">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="11" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="B24" s="29">
         <v>0.81</v>
@@ -22235,8 +22570,11 @@
       <c r="BE24" s="45">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.4">
+      <c r="BF24" s="34">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -22294,7 +22632,7 @@
       <c r="BC25" s="11"/>
       <c r="BD25" s="11"/>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:58">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -22353,9 +22691,9 @@
       <c r="BD26" s="28"/>
       <c r="BE26" s="28"/>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:58">
       <c r="A27" s="11" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -22412,6 +22750,7 @@
       <c r="BB27" s="11"/>
       <c r="BC27" s="11"/>
       <c r="BD27" s="11"/>
+      <c r="BF27" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
@@ -22423,40 +22762,40 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:BD17"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:BE17"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="84.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:57">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:56" ht="19.2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" ht="17.25">
       <c r="A2" s="17"/>
     </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:57">
       <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:56" ht="19.2" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" ht="17.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:57" ht="30.75" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.4">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57">
       <c r="A6" s="19"/>
     </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:57">
       <c r="A7" s="21" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -22505,9 +22844,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:57">
       <c r="A8" s="11" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -22556,179 +22895,182 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:57">
       <c r="A9" s="22" t="s">
-        <v>44</v>
+        <v>214</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="G9" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="23" t="s">
+      <c r="L9" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="23" t="s">
+      <c r="N9" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="23" t="s">
+      <c r="P9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="N9" s="23" t="s">
+      <c r="Q9" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="T9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="O9" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q9" s="23" t="s">
+      <c r="U9" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="V9" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y9" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="R9" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="S9" s="23" t="s">
+      <c r="Z9" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="T9" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="U9" s="23" t="s">
+      <c r="AA9" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="V9" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="X9" s="23" t="s">
+      <c r="AB9" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC9" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD9" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF9" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG9" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH9" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI9" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ9" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK9" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL9" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM9" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN9" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO9" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP9" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ9" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="AR9" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="Y9" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z9" s="23" t="s">
+      <c r="AS9" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="AA9" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB9" s="23" t="s">
+      <c r="AT9" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AC9" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD9" s="23" t="s">
+      <c r="AU9" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="AE9" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF9" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG9" s="23" t="s">
+      <c r="AV9" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW9" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="AH9" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="AI9" s="23" t="s">
+      <c r="AX9" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="AJ9" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK9" s="23" t="s">
+      <c r="AY9" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AL9" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM9" s="23" t="s">
+      <c r="AZ9" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AN9" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO9" s="23" t="s">
+      <c r="BA9" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AP9" s="23" t="s">
+      <c r="BB9" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC9" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AQ9" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="AR9" s="23" t="s">
+      <c r="BD9" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AS9" s="23" t="s">
+      <c r="BE9" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AT9" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AU9" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV9" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="AW9" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="AX9" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="AY9" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="AZ9" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="BA9" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="BB9" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="BC9" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="BD9" s="47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:57">
       <c r="A10" s="11" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="B10" s="24">
         <v>18.2</v>
@@ -22895,10 +23237,13 @@
       <c r="BD10" s="48">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.4">
+      <c r="BE10" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57">
       <c r="A11" s="11" t="s">
-        <v>55</v>
+        <v>216</v>
       </c>
       <c r="B11" s="24">
         <v>40.9</v>
@@ -23065,10 +23410,13 @@
       <c r="BD11" s="48">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.4">
+      <c r="BE11" s="24">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="B12" s="24">
         <v>27.3</v>
@@ -23235,10 +23583,13 @@
       <c r="BD12" s="48">
         <v>17.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.4">
+      <c r="BE12" s="24">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57">
       <c r="A13" s="11" t="s">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="B13" s="24">
         <v>9.1</v>
@@ -23405,10 +23756,13 @@
       <c r="BD13" s="48">
         <v>58.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.4">
+      <c r="BE13" s="24">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57">
       <c r="A14" s="11" t="s">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="B14" s="24">
         <v>4.5</v>
@@ -23575,8 +23929,11 @@
       <c r="BD14" s="48">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.4">
+      <c r="BE14" s="24">
+        <v>12.9032</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -23633,7 +23990,7 @@
       <c r="BB15" s="11"/>
       <c r="BC15" s="11"/>
     </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:57">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -23691,9 +24048,9 @@
       <c r="BC16" s="11"/>
       <c r="BD16" s="22"/>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:57">
       <c r="A17" s="42" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -23749,10 +24106,17 @@
       <c r="BA17" s="42"/>
       <c r="BB17" s="42"/>
       <c r="BC17" s="42"/>
+      <c r="BE17" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d0b21864-3105-44b5-88b9-2cedf9af7954}" enabled="1" method="Standard" siteId="{b9aaf114-bd80-4df3-b43d-ab54dd47f83f}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/expectations/Vaentingar_markadsadila.xlsx
+++ b/data/expectations/Vaentingar_markadsadila.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\HAGFRAEDISVID\Innlendir fjármálamarkaðir\4. Markaðskönnun\2026\Q1 19. -21. janúar\B3. Excel skjal fyrir vef - birtingarskjal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{544A60B5-DA87-4BEE-A3EA-2D591F780E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFA5823-5A3E-40D5-8A0E-616189C25FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,11 +26,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">I!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">II!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,7 +36,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -49,23 +45,583 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="220">
   <si>
+    <t>2012Q1</t>
+  </si>
+  <si>
     <t>Seðlabanki Íslands / Central Bank of Iceland</t>
   </si>
   <si>
-    <t>Birtingardagur / Date of publication: 28/1/2026</t>
+    <t xml:space="preserve">      Staðalfrávik / standard deviation</t>
   </si>
   <si>
-    <r>
-      <t>Örk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / Sheet</t>
-    </r>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Væntingakönnun markaðsaðila / Market expectations survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What do you think twelve-month inflation will measure, on average, in each quarter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the long-term nominal interest rate be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the long-term real interest rate be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be 24 months from now?</t>
+  </si>
+  <si>
+    <t>What do you think inflation will measure, on average, in each quarter?</t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be 12 months from now?</t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t>Væntingar til skamms tíma / Short-term expectations</t>
+  </si>
+  <si>
+    <t>Væntingar til langs tíma / Long-term expectations</t>
+  </si>
+  <si>
+    <t>In your opinion, what will the following economic variables be, on average, over the next 10 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Miðgildi / median</t>
+  </si>
+  <si>
+    <t>Long-term expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 12 mánuði? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 24 mánuði? </t>
+  </si>
+  <si>
+    <t>Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 5 ár? </t>
+  </si>
+  <si>
+    <t>Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 10 ár?</t>
+  </si>
+  <si>
+    <t>Væntingar til langs tíma</t>
+  </si>
+  <si>
+    <t>Heimild: Seðlabanki Íslands / Source: Central Bank of Iceland</t>
+  </si>
+  <si>
+    <t>Meðaltal /average</t>
+  </si>
+  <si>
+    <t>+1Q</t>
+  </si>
+  <si>
+    <t>+2Q</t>
+  </si>
+  <si>
+    <t>+3Q</t>
+  </si>
+  <si>
+    <t>+4Q</t>
+  </si>
+  <si>
+    <t>Miðgildi /median</t>
+  </si>
+  <si>
+    <t>Staðalfrávik /standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Meðaltal / average</t>
+  </si>
+  <si>
+    <t>núverandi ársfjórðungur / current quarter</t>
+  </si>
+  <si>
+    <t>2012Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What is your perception of the current monetary policy stance?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Hæfilegt / appropriate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 12 months from now?</t>
+  </si>
+  <si>
+    <t>2012Q3</t>
+  </si>
+  <si>
+    <t>Svarhlutfall / Participation rate</t>
+  </si>
+  <si>
+    <t>2012Q4</t>
+  </si>
+  <si>
+    <t>ISK/EUR</t>
+  </si>
+  <si>
+    <t>2013Q1</t>
+  </si>
+  <si>
+    <t>2013Q2</t>
+  </si>
+  <si>
+    <t>2013Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Of laust / too loose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Of þétt /  too tight</t>
+  </si>
+  <si>
+    <t>2013Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Alltof laust / far too loose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Alltof þétt / far too tight</t>
+  </si>
+  <si>
+    <t>2014Q1</t>
+  </si>
+  <si>
+    <t>2014Q2</t>
+  </si>
+  <si>
+    <t>2014Q3</t>
+  </si>
+  <si>
+    <t>2014Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 24 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate be, on average, over the next 5 years?</t>
+  </si>
+  <si>
+    <t>2015Q1</t>
+  </si>
+  <si>
+    <t>2015Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? </t>
+  </si>
+  <si>
+    <t>What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 2 / Question 2: </t>
+  </si>
+  <si>
+    <t>2015Q3</t>
+  </si>
+  <si>
+    <t>Meðaltal / average</t>
+  </si>
+  <si>
+    <t>Miðgildi / median</t>
+  </si>
+  <si>
+    <t>Staðalfrávik / standard deviation</t>
+  </si>
+  <si>
+    <t>2015Q4</t>
+  </si>
+  <si>
+    <t>2016Q1</t>
+  </si>
+  <si>
+    <t>2016Q2</t>
+  </si>
+  <si>
+    <t>2016Q3</t>
+  </si>
+  <si>
+    <t>2016Q4</t>
+  </si>
+  <si>
+    <t>2017Q1</t>
+  </si>
+  <si>
+    <t>2017Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 1/ Question 1: </t>
+  </si>
+  <si>
+    <t>Væntingar til skamms og meðallangs tíma</t>
+  </si>
+  <si>
+    <t>III-a</t>
+  </si>
+  <si>
+    <t>III-b</t>
+  </si>
+  <si>
+    <t>III-c</t>
+  </si>
+  <si>
+    <t>Short- and medium term expectations</t>
+  </si>
+  <si>
+    <t>Álit á taumhaldi peningastefnu Seðlabanka Íslands</t>
+  </si>
+  <si>
+    <t>Álit á taumhalds peningastefnu Seðlabanka Íslands / Opinion of the Central Bank of Iceland‘s monetary stance</t>
+  </si>
+  <si>
+    <t>Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir?</t>
+  </si>
+  <si>
+    <t>Spurning 5 / Question 5:</t>
+  </si>
+  <si>
+    <t>What is your perception of the current monetary policy stance?</t>
+  </si>
+  <si>
+    <t>Opinion of the Central Bank of Iceland‘s monetary stance</t>
+  </si>
+  <si>
+    <t>Væntingar til skamms og meðallangs tíma / Short- and medium-term expectations</t>
+  </si>
+  <si>
+    <t>Spurning 3a / Question 3a:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á  stöðu ársverðbólgu eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Hver er þín skoðun á gengi evru gagnvart krónu eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 12 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 3b / Question 3b: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu ársverðbólgu eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á gengi evru gagnvart krónu eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 24 mánuði? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spurning 3c / Question 3c: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 5 ár? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Hvað telur þú að skammtímanafnvextir verði að meðaltali næstu 5 ár? /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að skammtímaraunvextir verði að meðaltali næstu 5 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 10 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að langtímanafnvextir verði að meðaltali næstu 10 ár? / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hvað telur þú að langtímaraunvextir verði að meðaltali næstu 10 ár? /</t>
+  </si>
+  <si>
+    <t>Spurning 4 / Question 4:</t>
+  </si>
+  <si>
+    <t>2017Q3</t>
+  </si>
+  <si>
+    <t>2017Q4</t>
+  </si>
+  <si>
+    <t>2018Q1</t>
+  </si>
+  <si>
+    <t>2018Q2</t>
+  </si>
+  <si>
+    <t>2018Q3</t>
+  </si>
+  <si>
+    <t>2018Q4</t>
+  </si>
+  <si>
+    <t>2019Q1</t>
+  </si>
+  <si>
+    <t>2019Q2</t>
+  </si>
+  <si>
+    <t>2019Q3</t>
+  </si>
+  <si>
+    <t>Dagsetningar / Dates</t>
+  </si>
+  <si>
+    <t>2019Q4</t>
+  </si>
+  <si>
+    <t>2020Q1</t>
+  </si>
+  <si>
+    <t>2020Q2</t>
+  </si>
+  <si>
+    <t>2020Q3</t>
+  </si>
+  <si>
+    <t>2020Q4</t>
+  </si>
+  <si>
+    <t>2021Q1</t>
+  </si>
+  <si>
+    <t>2021Q2</t>
+  </si>
+  <si>
+    <t>2021Q3</t>
+  </si>
+  <si>
+    <t>2021Q4</t>
+  </si>
+  <si>
+    <t>2022Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 12 months from now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 24 months from now?</t>
+  </si>
+  <si>
+    <t>2022Q2</t>
+  </si>
+  <si>
+    <t>2022Q3</t>
+  </si>
+  <si>
+    <t>2022Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2023Q1</t>
+  </si>
+  <si>
+    <t>2023Q2</t>
+  </si>
+  <si>
+    <t>13.-17. feb. 2012</t>
+  </si>
+  <si>
+    <t>7.-11. maí 2012</t>
+  </si>
+  <si>
+    <t>13.-17. ágú. 2012</t>
+  </si>
+  <si>
+    <t>5.-9. nóv 2012</t>
+  </si>
+  <si>
+    <t>29. jan.-1. feb. 2013</t>
+  </si>
+  <si>
+    <t>6.-10. maí 2013</t>
+  </si>
+  <si>
+    <t>12.-15. ágúst 2013</t>
+  </si>
+  <si>
+    <t>28.-30. október 2013</t>
+  </si>
+  <si>
+    <t>3.-5. febrúar 2014</t>
+  </si>
+  <si>
+    <t>12.-14. maí 2014</t>
+  </si>
+  <si>
+    <t>11.-14 ágúst 2014</t>
+  </si>
+  <si>
+    <t>29.-31 október 2014</t>
+  </si>
+  <si>
+    <t>29.-30. janúar 2015</t>
+  </si>
+  <si>
+    <t>4.-6. maí 2015</t>
+  </si>
+  <si>
+    <t>10.-13. ágúst 2015</t>
+  </si>
+  <si>
+    <t>29. okt.-2. nóv. 2015</t>
+  </si>
+  <si>
+    <t>1.-3. febrúar 2016</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2016</t>
+  </si>
+  <si>
+    <t>8.-10. ágúst 2016</t>
+  </si>
+  <si>
+    <t>31. okt.-2. nóv. 2016</t>
+  </si>
+  <si>
+    <t>30. jan.-1. feb. 2017</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2017</t>
+  </si>
+  <si>
+    <t>9.-11. ágúst 2017</t>
+  </si>
+  <si>
+    <t>30. okt.-1. nóv. 2017</t>
+  </si>
+  <si>
+    <t>29.-31. janúar 2018</t>
+  </si>
+  <si>
+    <t>2.-4. maí 2018</t>
+  </si>
+  <si>
+    <t>13.-15. ágúst 2018</t>
+  </si>
+  <si>
+    <t>29.-31. október 2018</t>
+  </si>
+  <si>
+    <t>21.-23. janúar 2019</t>
+  </si>
+  <si>
+    <t>6.-8. maí 2019</t>
+  </si>
+  <si>
+    <t>12.-14. ágúst 2019</t>
+  </si>
+  <si>
+    <t>21.-23. október 2019</t>
+  </si>
+  <si>
+    <t>20.-22. janúar 2020</t>
+  </si>
+  <si>
+    <t>4.-6. maí 2020</t>
+  </si>
+  <si>
+    <t>10.-12. ágúst 2020</t>
+  </si>
+  <si>
+    <t>2.-4. nóvember 2020</t>
+  </si>
+  <si>
+    <t>18.-20. janúar 2021</t>
+  </si>
+  <si>
+    <t>3.-5. maí 2021</t>
+  </si>
+  <si>
+    <t>9.-11. ágúst 2021</t>
+  </si>
+  <si>
+    <t>1.-3. nóvember 2021</t>
+  </si>
+  <si>
+    <t>24.-26. janúar 2022</t>
+  </si>
+  <si>
+    <t>19.-22. apríl 2022</t>
+  </si>
+  <si>
+    <t>8.-10. ágúst 2022</t>
+  </si>
+  <si>
+    <t>7.-9. nóvember 2022</t>
+  </si>
+  <si>
+    <t>23.-25. janúar 2023</t>
+  </si>
+  <si>
+    <t>8.-10. maí 2023</t>
   </si>
   <si>
     <r>
@@ -82,367 +638,23 @@
     </r>
   </si>
   <si>
-    <t>Væntingar til skamms og meðallangs tíma</t>
+    <r>
+      <t>Örk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / Sheet</t>
+    </r>
   </si>
   <si>
-    <t>Short- and medium term expectations</t>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 12 mánuði? / </t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi?</t>
-  </si>
-  <si>
-    <t>What do you think inflation will measure, on average, in each quarter?</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? </t>
-  </si>
-  <si>
-    <t>What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
-  </si>
-  <si>
-    <t>III-a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 12 mánuði? </t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be 12 months from now?</t>
-  </si>
-  <si>
-    <t>III-b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hver er þín skoðun á stöðu eftirfarandi stærða eftir 24 mánuði? </t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be 24 months from now?</t>
-  </si>
-  <si>
-    <t>III-c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 5 ár? </t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t>Væntingar til langs tíma</t>
-  </si>
-  <si>
-    <t>Long-term expectations</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Hverjar telur þú að hagstærðirnar verði að meðaltali næstu 10 ár?</t>
-  </si>
-  <si>
-    <t>In your opinion, what will the following economic variables be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t>Álit á taumhaldi peningastefnu Seðlabanka Íslands</t>
-  </si>
-  <si>
-    <t>Opinion of the Central Bank of Iceland‘s monetary stance</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir?</t>
-  </si>
-  <si>
-    <t>What is your perception of the current monetary policy stance?</t>
-  </si>
-  <si>
-    <t>Svarhlutfall / Participation rate</t>
-  </si>
-  <si>
-    <t>Dagsetningar / Dates</t>
-  </si>
-  <si>
-    <t>2012Q1</t>
-  </si>
-  <si>
-    <t>13.-17. feb. 2012</t>
-  </si>
-  <si>
-    <t>2012Q2</t>
-  </si>
-  <si>
-    <t>7.-11. maí 2012</t>
-  </si>
-  <si>
-    <t>2012Q3</t>
-  </si>
-  <si>
-    <t>13.-17. ágú. 2012</t>
-  </si>
-  <si>
-    <t>2012Q4</t>
-  </si>
-  <si>
-    <t>5.-9. nóv 2012</t>
-  </si>
-  <si>
-    <t>2013Q1</t>
-  </si>
-  <si>
-    <t>29. jan.-1. feb. 2013</t>
-  </si>
-  <si>
-    <t>2013Q2</t>
-  </si>
-  <si>
-    <t>6.-10. maí 2013</t>
-  </si>
-  <si>
-    <t>2013Q3</t>
-  </si>
-  <si>
-    <t>12.-15. ágúst 2013</t>
-  </si>
-  <si>
-    <t>2013Q4</t>
-  </si>
-  <si>
-    <t>28.-30. október 2013</t>
-  </si>
-  <si>
-    <t>2014Q1</t>
-  </si>
-  <si>
-    <t>3.-5. febrúar 2014</t>
-  </si>
-  <si>
-    <t>2014Q2</t>
-  </si>
-  <si>
-    <t>12.-14. maí 2014</t>
-  </si>
-  <si>
-    <t>2014Q3</t>
-  </si>
-  <si>
-    <t>11.-14 ágúst 2014</t>
-  </si>
-  <si>
-    <t>2014Q4</t>
-  </si>
-  <si>
-    <t>29.-31 október 2014</t>
-  </si>
-  <si>
-    <t>2015Q1</t>
-  </si>
-  <si>
-    <t>29.-30. janúar 2015</t>
-  </si>
-  <si>
-    <t>2015Q2</t>
-  </si>
-  <si>
-    <t>4.-6. maí 2015</t>
-  </si>
-  <si>
-    <t>2015Q3</t>
-  </si>
-  <si>
-    <t>10.-13. ágúst 2015</t>
-  </si>
-  <si>
-    <t>2015Q4</t>
-  </si>
-  <si>
-    <t>29. okt.-2. nóv. 2015</t>
-  </si>
-  <si>
-    <t>2016Q1</t>
-  </si>
-  <si>
-    <t>1.-3. febrúar 2016</t>
-  </si>
-  <si>
-    <t>2016Q2</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2016</t>
-  </si>
-  <si>
-    <t>2016Q3</t>
-  </si>
-  <si>
-    <t>8.-10. ágúst 2016</t>
-  </si>
-  <si>
-    <t>2016Q4</t>
-  </si>
-  <si>
-    <t>31. okt.-2. nóv. 2016</t>
-  </si>
-  <si>
-    <t>2017Q1</t>
-  </si>
-  <si>
-    <t>30. jan.-1. feb. 2017</t>
-  </si>
-  <si>
-    <t>2017Q2</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2017</t>
-  </si>
-  <si>
-    <t>2017Q3</t>
-  </si>
-  <si>
-    <t>9.-11. ágúst 2017</t>
-  </si>
-  <si>
-    <t>2017Q4</t>
-  </si>
-  <si>
-    <t>30. okt.-1. nóv. 2017</t>
-  </si>
-  <si>
-    <t>2018Q1</t>
-  </si>
-  <si>
-    <t>29.-31. janúar 2018</t>
-  </si>
-  <si>
-    <t>2018Q2</t>
-  </si>
-  <si>
-    <t>2.-4. maí 2018</t>
-  </si>
-  <si>
-    <t>2018Q3</t>
-  </si>
-  <si>
-    <t>13.-15. ágúst 2018</t>
-  </si>
-  <si>
-    <t>2018Q4</t>
-  </si>
-  <si>
-    <t>29.-31. október 2018</t>
-  </si>
-  <si>
-    <t>2019Q1</t>
-  </si>
-  <si>
-    <t>21.-23. janúar 2019</t>
-  </si>
-  <si>
-    <t>2019Q2</t>
-  </si>
-  <si>
-    <t>6.-8. maí 2019</t>
-  </si>
-  <si>
-    <t>2019Q3</t>
-  </si>
-  <si>
-    <t>12.-14. ágúst 2019</t>
-  </si>
-  <si>
-    <t>2019Q4</t>
-  </si>
-  <si>
-    <t>21.-23. október 2019</t>
-  </si>
-  <si>
-    <t>2020Q1</t>
-  </si>
-  <si>
-    <t>20.-22. janúar 2020</t>
-  </si>
-  <si>
-    <t>2020Q2</t>
-  </si>
-  <si>
-    <t>4.-6. maí 2020</t>
-  </si>
-  <si>
-    <t>2020Q3</t>
-  </si>
-  <si>
-    <t>10.-12. ágúst 2020</t>
-  </si>
-  <si>
-    <t>2020Q4</t>
-  </si>
-  <si>
-    <t>2.-4. nóvember 2020</t>
-  </si>
-  <si>
-    <t>2021Q1</t>
-  </si>
-  <si>
-    <t>18.-20. janúar 2021</t>
-  </si>
-  <si>
-    <t>2021Q2</t>
-  </si>
-  <si>
-    <t>3.-5. maí 2021</t>
-  </si>
-  <si>
-    <t>2021Q3</t>
-  </si>
-  <si>
-    <t>9.-11. ágúst 2021</t>
-  </si>
-  <si>
-    <t>2021Q4</t>
-  </si>
-  <si>
-    <t>1.-3. nóvember 2021</t>
-  </si>
-  <si>
-    <t>2022Q1</t>
-  </si>
-  <si>
-    <t>24.-26. janúar 2022</t>
-  </si>
-  <si>
-    <t>2022Q2</t>
-  </si>
-  <si>
-    <t>19.-22. apríl 2022</t>
-  </si>
-  <si>
-    <t>2022Q3</t>
-  </si>
-  <si>
-    <t>8.-10. ágúst 2022</t>
-  </si>
-  <si>
-    <t>2022Q4</t>
-  </si>
-  <si>
-    <t>7.-9. nóvember 2022</t>
-  </si>
-  <si>
-    <t>2023Q1</t>
-  </si>
-  <si>
-    <t>23.-25. janúar 2023</t>
-  </si>
-  <si>
-    <t>2023Q2</t>
-  </si>
-  <si>
-    <t>8.-10. maí 2023</t>
+    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 12 mánuði? / </t>
   </si>
   <si>
     <t>2023Q3</t>
@@ -499,10 +711,10 @@
     <t>11.-13. ágúst 2025</t>
   </si>
   <si>
-    <t>2025Q4</t>
+    <t>3. til 5. nóvember 2025</t>
   </si>
   <si>
-    <t>3. til 5. nóvember 2025</t>
+    <t>2025Q4</t>
   </si>
   <si>
     <t>2026Q1</t>
@@ -511,223 +723,7 @@
     <t>19. til 21. janúar 2026</t>
   </si>
   <si>
-    <t>Væntingakönnun markaðsaðila / Market expectations survey</t>
-  </si>
-  <si>
-    <t>Væntingar til skamms og meðallangs tíma / Short- and medium-term expectations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 1/ Question 1: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver telur þú að ársverðbólga verði að meðaltali í hverjum ársfjórðungi? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What do you think twelve-month inflation will measure, on average, in each quarter?</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Meðaltal / average</t>
-  </si>
-  <si>
-    <t>núverandi ársfjórðungur / current quarter</t>
-  </si>
-  <si>
-    <t>+1Q</t>
-  </si>
-  <si>
-    <t>+2Q</t>
-  </si>
-  <si>
-    <t>+3Q</t>
-  </si>
-  <si>
-    <t>+4Q</t>
-  </si>
-  <si>
-    <t>Miðgildi / median</t>
-  </si>
-  <si>
-    <t>Staðalfrávik / standard deviation</t>
-  </si>
-  <si>
-    <t>Heimild: Seðlabanki Íslands / Source: Central Bank of Iceland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 2 / Question 2: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hverjir telur þú að veðlánavextir Seðlabanka Íslands verði í lok hvers ársfjórðungs? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What do you think the Central Bank of Iceland collateralized lending rate will be at the end of each quarter?</t>
-  </si>
-  <si>
-    <t>Meðaltal /average</t>
-  </si>
-  <si>
-    <t>Miðgildi /median</t>
-  </si>
-  <si>
-    <t>Staðalfrávik /standard deviation</t>
-  </si>
-  <si>
-    <t>Væntingar til skamms tíma / Short-term expectations</t>
-  </si>
-  <si>
-    <t>Spurning 3a / Question 3a:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á  stöðu ársverðbólgu eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Meðaltal / average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Miðgildi / median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Staðalfrávik / standard deviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Hver er þín skoðun á gengi evru gagnvart krónu eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 12 months from now?</t>
-  </si>
-  <si>
-    <t>ISK/EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 12 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 12 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 3b / Question 3b: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu ársverðbólgu eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á gengi evru gagnvart krónu eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the EURISK exchange rate be 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu veðlánavaxta SÍ eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the CBI collateralized lending rate be 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímanafnvaxta eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hver er þín skoðun á stöðu skammtímaraunvaxta eftir 24 mánuði? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate 24 months from now?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spurning 3c / Question 3c: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 5 ár? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Hvað telur þú að skammtímanafnvextir verði að meðaltali næstu 5 ár? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term nominal interest rate be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að skammtímaraunvextir verði að meðaltali næstu 5 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the short-term real interest rate be, on average, over the next 5 years?</t>
-  </si>
-  <si>
-    <t>Væntingar til langs tíma / Long-term expectations</t>
-  </si>
-  <si>
-    <t>Spurning 4 / Question 4:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að ársverðbólga verði að meðaltali næstu 10 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the twelve-month inflation be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að langtímanafnvextir verði að meðaltali næstu 10 ár? / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the long-term nominal interest rate be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvað telur þú að langtímaraunvextir verði að meðaltali næstu 10 ár? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In your opinion, what will the long-term real interest rate be, on average, over the next 10 years?</t>
-  </si>
-  <si>
-    <t>Álit á taumhalds peningastefnu Seðlabanka Íslands / Opinion of the Central Bank of Iceland‘s monetary stance</t>
-  </si>
-  <si>
-    <t>Spurning 5 / Question 5:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Hvert álítur þú taumhald peningastefnunnar vera um þessar mundir? /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   What is your perception of the current monetary policy stance?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Alltof laust / far too loose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Of laust / too loose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Hæfilegt / appropriate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Of þétt /  too tight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Alltof þétt / far too tight</t>
+    <t>Birtingardagur / Date of publication: 28/1/2026</t>
   </si>
 </sst>
 </file>
@@ -735,14 +731,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1374,10 +1370,10 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1441,11 +1437,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1463,8 +1459,8 @@
     <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1851,7 +1847,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:G79"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
@@ -1860,769 +1856,769 @@
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C1" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="17.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
-        <v>2</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" ht="15" customHeight="1">
-      <c r="C8" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="B9" s="9" t="s">
-        <v>6</v>
-      </c>
       <c r="C9" s="12" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="15" customHeight="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="9" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="15" customHeight="1"/>
-    <row r="15" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="17" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="18" spans="2:4" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="15" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="15" customHeight="1"/>
-    <row r="22" spans="2:4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C23" s="10">
         <v>0.78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C24" s="10">
         <v>0.63</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C25" s="10">
         <v>0.69</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="9" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C26" s="10">
         <v>0.64</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C27" s="10">
         <v>0.67</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C28" s="10">
         <v>0.69</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C29" s="10">
         <v>0.64</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C30" s="10">
         <v>0.56000000000000005</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="9" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C31" s="10">
         <v>0.59</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C32" s="10">
         <v>0.74</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="9" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C33" s="10">
         <v>0.61</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C34" s="10">
         <v>0.68</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C35" s="10">
         <v>0.59</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C36" s="10">
         <v>0.57999999999999996</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="9" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C37" s="10">
         <v>0.6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="9" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C38" s="10">
         <v>0.45</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C39" s="10">
         <v>0.59</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C40" s="10">
         <v>0.41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="9" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C41" s="10">
         <v>0.66</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="9" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C42" s="10">
         <v>0.66</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C43" s="10">
         <v>0.56999999999999995</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C44" s="10">
         <v>0.73</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="9" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C45" s="10">
         <v>0.6</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="9" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C46" s="10">
         <v>0.77</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="9" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C47" s="10">
         <v>0.83</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="9" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C48" s="10">
         <v>0.72</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="9" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C49" s="10">
         <v>0.7</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C50" s="10">
         <v>0.93</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="9" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="C51" s="10">
         <v>0.75</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="9" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C52" s="10">
         <v>0.82</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="9" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C53" s="10">
         <v>0.86</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="9" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C54" s="10">
         <v>0.89</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="9" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C55" s="10">
         <v>0.86</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="9" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C56" s="10">
         <v>0.96</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B57" s="9" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C57" s="10">
         <v>0.86</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B58" s="9" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C58" s="10">
         <v>0.9</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B59" s="9" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C59" s="10">
         <v>0.9</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B60" s="9" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C60" s="10">
         <v>0.9</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B61" s="9" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C61" s="10">
         <v>0.83</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B62" s="9" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C62" s="10">
         <v>0.86206896551724133</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B63" s="9" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C63" s="10">
         <v>0.86</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B64" s="9" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C64" s="10">
         <v>0.8</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" s="9" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C65" s="10">
         <v>0.77</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" s="9" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C66" s="10">
         <v>0.92</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" s="9" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C67" s="10">
         <v>0.84</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B68" s="9" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C68" s="10">
         <v>0.79</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" s="9" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="C69" s="10">
         <v>0.71</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B70" s="9" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="C70" s="10">
         <v>0.79</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" s="9" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="C71" s="10">
         <v>0.7</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B72" s="9" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C72" s="10">
         <v>0.81</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" s="9" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="C73" s="10">
         <v>0.69</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B74" s="9" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="C74" s="10">
         <v>0.79</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" s="9" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="C75" s="10">
         <v>0.77</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B76" s="9" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="C76" s="10">
         <v>0.64102564102564108</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" s="9" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="C77" s="10">
         <v>0.76</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B78" s="9" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="C78" s="10">
         <v>0.78947368421052633</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" s="9" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="C79" s="10">
         <v>0.79</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>146</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2648,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:BF33"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
@@ -2668,14 +2664,14 @@
     <col min="58" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -2685,15 +2681,15 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:58" ht="17.25">
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -2742,9 +2738,9 @@
       <c r="AT6" s="11"/>
       <c r="AU6" s="11"/>
     </row>
-    <row r="7" spans="1:58">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2793,9 +2789,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>150</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2844,9 +2840,9 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -2905,10 +2901,10 @@
       <c r="BD9" s="22"/>
       <c r="BE9" s="22"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="8" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -2966,185 +2962,185 @@
       <c r="BD10" s="11"/>
       <c r="BF10" s="51"/>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K11" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M11" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N11" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O11" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P11" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R11" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S11" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T11" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U11" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V11" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W11" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X11" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z11" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB11" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC11" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD11" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE11" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF11" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG11" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH11" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI11" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ11" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK11" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL11" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM11" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN11" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO11" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP11" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ11" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR11" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS11" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT11" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU11" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV11" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW11" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX11" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY11" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ11" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA11" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB11" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC11" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD11" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE11" s="26" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF11" s="26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B12" s="29">
         <v>5.89</v>
@@ -3318,9 +3314,9 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B13" s="29">
         <v>5.17</v>
@@ -3494,9 +3490,9 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B14" s="29">
         <v>5.07</v>
@@ -3670,9 +3666,9 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B15" s="24">
         <v>4.95</v>
@@ -3846,9 +3842,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B16" s="29">
         <v>4.71</v>
@@ -4022,7 +4018,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="37"/>
       <c r="B17" s="29"/>
       <c r="C17" s="11"/>
@@ -4082,185 +4078,185 @@
       <c r="BE17" s="34"/>
       <c r="BF17" s="34"/>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M18" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N18" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O18" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P18" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R18" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S18" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T18" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U18" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V18" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W18" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X18" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y18" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z18" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB18" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC18" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD18" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE18" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF18" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG18" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH18" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI18" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ18" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK18" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL18" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM18" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN18" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO18" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP18" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ18" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR18" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS18" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT18" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU18" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV18" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW18" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX18" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY18" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ18" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA18" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB18" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC18" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD18" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE18" s="44" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF18" s="44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B19" s="24">
         <v>6.15</v>
@@ -4434,9 +4430,9 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B20" s="29">
         <v>5.5</v>
@@ -4610,9 +4606,9 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B21" s="29">
         <v>5.0999999999999996</v>
@@ -4786,9 +4782,9 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B22" s="24">
         <v>5.15</v>
@@ -4962,9 +4958,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B23" s="24">
         <v>4.8499999999999996</v>
@@ -5138,7 +5134,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="29"/>
       <c r="C24" s="11"/>
@@ -5198,185 +5194,185 @@
       <c r="BE24" s="34"/>
       <c r="BF24" s="34"/>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M25" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N25" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P25" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R25" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S25" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T25" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U25" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V25" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W25" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X25" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y25" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z25" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB25" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC25" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD25" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE25" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF25" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG25" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH25" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI25" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ25" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK25" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL25" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM25" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN25" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO25" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP25" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ25" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR25" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS25" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT25" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU25" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV25" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW25" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX25" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY25" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ25" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA25" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB25" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC25" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD25" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE25" s="44" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF25" s="44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B26" s="29">
         <v>1.01</v>
@@ -5550,9 +5546,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B27" s="29">
         <v>1.24</v>
@@ -5726,9 +5722,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B28" s="29">
         <v>1.19</v>
@@ -5902,9 +5898,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:58">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B29" s="29">
         <v>1.34</v>
@@ -6078,9 +6074,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:58">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B30" s="29">
         <v>1.1399999999999999</v>
@@ -6254,7 +6250,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:58">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -6313,9 +6309,9 @@
       <c r="BD31" s="22"/>
       <c r="BE31" s="22"/>
     </row>
-    <row r="32" spans="1:58">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6369,7 +6365,7 @@
       <c r="AY32" s="11"/>
       <c r="BF32" s="51"/>
     </row>
-    <row r="33" spans="1:48">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6430,7 +6426,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:BF33"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -6446,25 +6442,25 @@
     <col min="58" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -6513,9 +6509,9 @@
       <c r="AT6" s="11"/>
       <c r="AU6" s="11"/>
     </row>
-    <row r="7" spans="1:58">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -6564,9 +6560,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -6615,9 +6611,9 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -6672,10 +6668,10 @@
       <c r="AZ9" s="22"/>
       <c r="BA9" s="22"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="43" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -6734,185 +6730,185 @@
       <c r="BE10" s="42"/>
       <c r="BF10" s="51"/>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K11" s="35" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O11" s="35" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="35" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S11" s="35" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T11" s="35" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U11" s="35" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W11" s="35" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X11" s="35" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="35" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z11" s="35" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA11" s="35" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB11" s="35" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC11" s="35" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD11" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE11" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF11" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG11" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH11" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI11" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ11" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK11" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL11" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM11" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN11" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO11" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP11" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ11" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR11" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS11" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT11" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU11" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV11" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW11" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX11" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY11" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ11" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA11" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB11" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC11" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD11" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE11" s="47" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF11" s="26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B12" s="29">
         <v>4.91</v>
@@ -7086,9 +7082,9 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B13" s="29">
         <v>5.1100000000000003</v>
@@ -7262,9 +7258,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B14" s="29">
         <v>5.38</v>
@@ -7438,9 +7434,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B15" s="29">
         <v>5.53</v>
@@ -7614,9 +7610,9 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B16" s="29">
         <v>5.73</v>
@@ -7790,7 +7786,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="37"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7850,185 +7846,185 @@
       <c r="BE17" s="49"/>
       <c r="BF17" s="34"/>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K18" s="35" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L18" s="35" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N18" s="35" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O18" s="35" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P18" s="35" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R18" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S18" s="35" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T18" s="35" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U18" s="35" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W18" s="35" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X18" s="35" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y18" s="35" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z18" s="35" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA18" s="35" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB18" s="35" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC18" s="35" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD18" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE18" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF18" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG18" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH18" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI18" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ18" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK18" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL18" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM18" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN18" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO18" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP18" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ18" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR18" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS18" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT18" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU18" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV18" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW18" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX18" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY18" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ18" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA18" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB18" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC18" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD18" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE18" s="47" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF18" s="44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B19" s="29">
         <v>5</v>
@@ -8202,9 +8198,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B20" s="29">
         <v>5</v>
@@ -8378,9 +8374,9 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B21" s="24">
         <v>5.25</v>
@@ -8554,9 +8550,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B22" s="29">
         <v>5.37</v>
@@ -8730,9 +8726,9 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B23" s="24">
         <v>5.75</v>
@@ -8906,7 +8902,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8966,185 +8962,185 @@
       <c r="BE24" s="49"/>
       <c r="BF24" s="34"/>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K25" s="35" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L25" s="35" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M25" s="35" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N25" s="35" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O25" s="35" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P25" s="35" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="35" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R25" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S25" s="35" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T25" s="35" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U25" s="35" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V25" s="35" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W25" s="35" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X25" s="35" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y25" s="35" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z25" s="35" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA25" s="35" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB25" s="35" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC25" s="35" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD25" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE25" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF25" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG25" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH25" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI25" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ25" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK25" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL25" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM25" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN25" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO25" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP25" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ25" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR25" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS25" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT25" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU25" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV25" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW25" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX25" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY25" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ25" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA25" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB25" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC25" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD25" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE25" s="50" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF25" s="44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B26" s="29">
         <v>0.16</v>
@@ -9318,9 +9314,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="B27" s="29">
         <v>0.27</v>
@@ -9494,9 +9490,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="B28" s="29">
         <v>0.46</v>
@@ -9670,9 +9666,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" spans="1:58">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B29" s="29">
         <v>0.68</v>
@@ -9846,9 +9842,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:58">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B30" s="29">
         <v>0.76</v>
@@ -10022,7 +10018,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:58">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -10081,9 +10077,9 @@
       <c r="BD31" s="22"/>
       <c r="BE31" s="27"/>
     </row>
-    <row r="32" spans="1:58">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -10138,7 +10134,7 @@
       <c r="AZ32" s="11"/>
       <c r="BF32" s="51"/>
     </row>
-    <row r="33" spans="1:47">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10200,207 +10196,207 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF39"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z6" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB6" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD6" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF6" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG6" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR6" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS6" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT6" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW6" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX6" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY6" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ6" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA6" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB6" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC6" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD6" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE6" s="50" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF6" s="50" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10459,9 +10455,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -10520,12 +10516,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>171</v>
+        <v>11</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
@@ -10583,9 +10579,9 @@
       <c r="BD9" s="33"/>
       <c r="BE9" s="33"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B10" s="34">
         <v>4.99</v>
@@ -10759,9 +10755,9 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B11" s="34">
         <v>5</v>
@@ -10935,9 +10931,9 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B12" s="34">
         <v>0.84</v>
@@ -11111,7 +11107,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -11171,9 +11167,9 @@
       <c r="BE13" s="48"/>
       <c r="BF13" s="34"/>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -11233,12 +11229,12 @@
       <c r="BE14" s="48"/>
       <c r="BF14" s="34"/>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
@@ -11297,9 +11293,9 @@
       <c r="BE15" s="33"/>
       <c r="BF15" s="34"/>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B16" s="34">
         <v>164.72</v>
@@ -11473,9 +11469,9 @@
         <v>148.6</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B17" s="34">
         <v>165</v>
@@ -11649,9 +11645,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B18" s="34">
         <v>5.65</v>
@@ -11825,7 +11821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:58">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -11885,9 +11881,9 @@
       <c r="BE19" s="48"/>
       <c r="BF19" s="34"/>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -11947,12 +11943,12 @@
       <c r="BE20" s="48"/>
       <c r="BF20" s="34"/>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C21" s="33"/>
       <c r="D21" s="33"/>
@@ -12011,9 +12007,9 @@
       <c r="BE21" s="33"/>
       <c r="BF21" s="34"/>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B22" s="34">
         <v>5.73</v>
@@ -12187,9 +12183,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B23" s="34">
         <v>5.5</v>
@@ -12363,9 +12359,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B24" s="34">
         <v>1.02</v>
@@ -12539,7 +12535,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -12599,9 +12595,9 @@
       <c r="BE25" s="48"/>
       <c r="BF25" s="34"/>
     </row>
-    <row r="26" spans="1:58">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -12652,12 +12648,12 @@
       <c r="BE26" s="48"/>
       <c r="BF26" s="34"/>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="33"/>
@@ -12716,9 +12712,9 @@
       <c r="BE27" s="33"/>
       <c r="BF27" s="34"/>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -12868,9 +12864,9 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="29" spans="1:58">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -13020,9 +13016,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="30" spans="1:58">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -13172,7 +13168,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:58">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -13232,9 +13228,9 @@
       <c r="BE31" s="49"/>
       <c r="BF31" s="34"/>
     </row>
-    <row r="32" spans="1:58">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -13294,12 +13290,12 @@
       <c r="BE32" s="49"/>
       <c r="BF32" s="34"/>
     </row>
-    <row r="33" spans="1:58">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
@@ -13358,9 +13354,9 @@
       <c r="BE33" s="33"/>
       <c r="BF33" s="34"/>
     </row>
-    <row r="34" spans="1:58">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -13510,9 +13506,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:58">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -13662,9 +13658,9 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="36" spans="1:58">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -13814,7 +13810,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="37" spans="1:58">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -13874,7 +13870,7 @@
       <c r="BE37" s="22"/>
       <c r="BF37" s="34"/>
     </row>
-    <row r="38" spans="1:58">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -13933,9 +13929,9 @@
       <c r="BD38" s="11"/>
       <c r="BF38" s="51"/>
     </row>
-    <row r="39" spans="1:58">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -13997,212 +13993,212 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z6" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB6" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD6" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF6" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG6" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR6" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS6" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT6" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW6" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX6" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY6" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ6" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA6" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB6" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC6" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD6" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE6" s="47" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF6" s="47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -14261,9 +14257,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -14322,12 +14318,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
@@ -14385,9 +14381,9 @@
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B10" s="24">
         <v>4.68</v>
@@ -14561,9 +14557,9 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B11" s="24">
         <v>5</v>
@@ -14737,9 +14733,9 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B12" s="24">
         <v>0.89</v>
@@ -14913,7 +14909,7 @@
         <v>0.39989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -14973,9 +14969,9 @@
       <c r="BE13" s="49"/>
       <c r="BF13" s="34"/>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -15035,12 +15031,12 @@
       <c r="BE14" s="49"/>
       <c r="BF14" s="34"/>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
@@ -15099,9 +15095,9 @@
       <c r="BE15" s="28"/>
       <c r="BF15" s="34"/>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B16" s="24">
         <v>167.65</v>
@@ -15275,9 +15271,9 @@
         <v>149.9</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B17" s="24">
         <v>168.5</v>
@@ -15451,9 +15447,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B18" s="24">
         <v>10.94</v>
@@ -15627,7 +15623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:58">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -15687,9 +15683,9 @@
       <c r="BE19" s="49"/>
       <c r="BF19" s="34"/>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -15749,12 +15745,12 @@
       <c r="BE20" s="49"/>
       <c r="BF20" s="34"/>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -15813,9 +15809,9 @@
       <c r="BE21" s="28"/>
       <c r="BF21" s="34"/>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B22" s="24">
         <v>6.41</v>
@@ -15989,9 +15985,9 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B23" s="24">
         <v>6.13</v>
@@ -16165,9 +16161,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B24" s="24">
         <v>1.34</v>
@@ -16341,7 +16337,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -16401,9 +16397,9 @@
       <c r="BE25" s="49"/>
       <c r="BF25" s="34"/>
     </row>
-    <row r="26" spans="1:58">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -16463,12 +16459,12 @@
       <c r="BE26" s="49"/>
       <c r="BF26" s="34"/>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
@@ -16482,7 +16478,7 @@
       <c r="L27" s="28"/>
       <c r="M27" s="28"/>
       <c r="N27" s="28" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="O27" s="28"/>
       <c r="P27" s="28"/>
@@ -16529,9 +16525,9 @@
       <c r="BE27" s="28"/>
       <c r="BF27" s="34"/>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -16681,9 +16677,9 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="29" spans="1:58">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -16833,9 +16829,9 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="30" spans="1:58">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -16985,7 +16981,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:58">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
@@ -17045,9 +17041,9 @@
       <c r="BE31" s="49"/>
       <c r="BF31" s="34"/>
     </row>
-    <row r="32" spans="1:58">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -17107,12 +17103,12 @@
       <c r="BE32" s="49"/>
       <c r="BF32" s="34"/>
     </row>
-    <row r="33" spans="1:58">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -17171,9 +17167,9 @@
       <c r="BE33" s="28"/>
       <c r="BF33" s="34"/>
     </row>
-    <row r="34" spans="1:58">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
@@ -17323,9 +17319,9 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="35" spans="1:58">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
@@ -17475,9 +17471,9 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="36" spans="1:58">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -17627,7 +17623,7 @@
         <v>0.75249999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:58">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A37" s="22"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -17686,7 +17682,7 @@
       <c r="BD37" s="28"/>
       <c r="BE37" s="28"/>
     </row>
-    <row r="38" spans="1:58">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -17738,9 +17734,9 @@
       <c r="AW38" s="11"/>
       <c r="BF38" s="51"/>
     </row>
-    <row r="39" spans="1:58">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -17791,7 +17787,7 @@
       <c r="AV39" s="11"/>
       <c r="AW39" s="11"/>
     </row>
-    <row r="40" spans="1:58">
+    <row r="40" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A40" s="32"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -17855,7 +17851,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="15" width="11.42578125" style="1" customWidth="1"/>
@@ -17863,201 +17859,201 @@
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z6" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB6" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD6" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF6" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG6" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR6" s="26" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AS6" s="26" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AT6" s="26" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="26" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="26" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AW6" s="26" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AX6" s="26" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AY6" s="26" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AZ6" s="26" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="BA6" s="26" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BB6" s="26" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BC6" s="26" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BD6" s="26" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BE6" s="47" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BF6" s="47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:58">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -18116,9 +18112,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="49"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -18177,12 +18173,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="49"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>198</v>
+        <v>10</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -18241,9 +18237,9 @@
       <c r="BE9" s="28"/>
       <c r="BF9" s="53"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B10" s="24">
         <v>4.55</v>
@@ -18417,9 +18413,9 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B11" s="29">
         <v>4.8</v>
@@ -18593,9 +18589,9 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B12" s="24">
         <v>0.85</v>
@@ -18769,7 +18765,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="24"/>
       <c r="C13" s="29"/>
@@ -18829,9 +18825,9 @@
       <c r="BE13" s="48"/>
       <c r="BF13" s="34"/>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -18891,12 +18887,12 @@
       <c r="BE14" s="49"/>
       <c r="BF14" s="11"/>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -18955,9 +18951,9 @@
       <c r="BE15" s="28"/>
       <c r="BF15" s="24"/>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -19107,9 +19103,9 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -19259,9 +19255,9 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
@@ -19411,7 +19407,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="19" spans="1:58">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -19471,9 +19467,9 @@
       <c r="BE19" s="49"/>
       <c r="BF19" s="11"/>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19533,12 +19529,12 @@
       <c r="BE20" s="49"/>
       <c r="BF20" s="11"/>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
@@ -19597,9 +19593,9 @@
       <c r="BE21" s="28"/>
       <c r="BF21" s="24"/>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -19749,9 +19745,9 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -19901,9 +19897,9 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="29"/>
@@ -20053,7 +20049,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -20113,7 +20109,7 @@
       <c r="BE25" s="28"/>
       <c r="BF25" s="24"/>
     </row>
-    <row r="26" spans="1:58">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -20165,9 +20161,9 @@
       <c r="AW26" s="11"/>
       <c r="BF26" s="51"/>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -20217,7 +20213,7 @@
       <c r="AU27" s="11"/>
       <c r="AV27" s="11"/>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
     </row>
   </sheetData>
@@ -20233,7 +20229,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="15" width="11.85546875" style="1" customWidth="1"/>
@@ -20241,201 +20237,201 @@
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Z6" s="26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB6" s="26" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AD6" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="26" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AF6" s="26" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AG6" s="26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="26" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="26" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="26" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="26" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="26" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="26" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="26" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="26" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="26" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AR6" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT6" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AU6" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="AV6" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="AW6" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX6" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="AY6" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="AZ6" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="BA6" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="BB6" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="BC6" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="BD6" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="BE6" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="BF6" s="47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>117</v>
-      </c>
-      <c r="AS6" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="AT6" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="AU6" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV6" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="AX6" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY6" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="AZ6" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="BB6" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="BC6" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="BD6" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="BE6" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="BF6" s="47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:58">
-      <c r="A7" s="21" t="s">
-        <v>204</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -20494,9 +20490,9 @@
       <c r="BD7" s="11"/>
       <c r="BE7" s="46"/>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -20555,12 +20551,12 @@
       <c r="BD8" s="11"/>
       <c r="BE8" s="46"/>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -20618,9 +20614,9 @@
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B10" s="29">
         <v>4.32</v>
@@ -20794,9 +20790,9 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B11" s="29">
         <v>4.5</v>
@@ -20970,9 +20966,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B12" s="29">
         <v>0.82</v>
@@ -21146,7 +21142,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -21206,9 +21202,9 @@
       <c r="BE13" s="46"/>
       <c r="BF13" s="34"/>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>207</v>
+        <v>115</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -21268,12 +21264,12 @@
       <c r="BE14" s="46"/>
       <c r="BF14" s="34"/>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>208</v>
+        <v>15</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -21332,9 +21328,9 @@
       <c r="BE15" s="28"/>
       <c r="BF15" s="34"/>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B16" s="29">
         <v>7.02</v>
@@ -21508,9 +21504,9 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B17" s="29">
         <v>7.05</v>
@@ -21684,9 +21680,9 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B18" s="29">
         <v>1.03</v>
@@ -21860,7 +21856,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:58">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -21920,9 +21916,9 @@
       <c r="BE19" s="46"/>
       <c r="BF19" s="34"/>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -21982,12 +21978,12 @@
       <c r="BE20" s="46"/>
       <c r="BF20" s="34"/>
     </row>
-    <row r="21" spans="1:58">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>210</v>
+        <v>16</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
@@ -22046,9 +22042,9 @@
       <c r="BE21" s="28"/>
       <c r="BF21" s="34"/>
     </row>
-    <row r="22" spans="1:58">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B22" s="29">
         <v>2.23</v>
@@ -22222,9 +22218,9 @@
         <v>2.5032999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:58">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B23" s="29">
         <v>2.37</v>
@@ -22398,9 +22394,9 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="24" spans="1:58">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="B24" s="29">
         <v>0.81</v>
@@ -22574,7 +22570,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:58">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -22632,7 +22628,7 @@
       <c r="BC25" s="11"/>
       <c r="BD25" s="11"/>
     </row>
-    <row r="26" spans="1:58">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -22691,9 +22687,9 @@
       <c r="BD26" s="28"/>
       <c r="BE26" s="28"/>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -22763,39 +22759,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:BE17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84.7109375" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:57" ht="17.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
     </row>
-    <row r="3" spans="1:57">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" ht="17.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:57" ht="30.75" customHeight="1">
+    <row r="5" spans="1:57" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A6" s="19"/>
     </row>
-    <row r="7" spans="1:57">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -22844,9 +22840,9 @@
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
     </row>
-    <row r="8" spans="1:57">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -22895,182 +22891,182 @@
       <c r="AT8" s="11"/>
       <c r="AU8" s="11"/>
     </row>
-    <row r="9" spans="1:57">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>214</v>
+        <v>44</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="T9" s="23" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U9" s="23" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AA9" s="23" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="AB9" s="23" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="AH9" s="23" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AI9" s="23" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AJ9" s="23" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AK9" s="23" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AL9" s="23" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AM9" s="23" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AN9" s="23" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="AO9" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="AP9" s="23" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AQ9" s="23" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="AR9" s="23" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AS9" s="23" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AT9" s="23" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AU9" s="23" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="AV9" s="23" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="AW9" s="23" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AX9" s="23" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="AY9" s="23" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="AZ9" s="23" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="BA9" s="23" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="BB9" s="23" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="BC9" s="23" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="BD9" s="47" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="BE9" s="47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:57">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="B10" s="24">
         <v>18.2</v>
@@ -23241,9 +23237,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:57">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="B11" s="24">
         <v>40.9</v>
@@ -23414,9 +23410,9 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:57">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="B12" s="24">
         <v>27.3</v>
@@ -23587,9 +23583,9 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="13" spans="1:57">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="B13" s="24">
         <v>9.1</v>
@@ -23760,9 +23756,9 @@
         <v>41.9</v>
       </c>
     </row>
-    <row r="14" spans="1:57">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>219</v>
+        <v>59</v>
       </c>
       <c r="B14" s="24">
         <v>4.5</v>
@@ -23933,7 +23929,7 @@
         <v>12.9032</v>
       </c>
     </row>
-    <row r="15" spans="1:57">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -23990,7 +23986,7 @@
       <c r="BB15" s="11"/>
       <c r="BC15" s="11"/>
     </row>
-    <row r="16" spans="1:57">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -24048,9 +24044,9 @@
       <c r="BC16" s="11"/>
       <c r="BD16" s="22"/>
     </row>
-    <row r="17" spans="1:57">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A17" s="42" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
